--- a/database/event/8040/event_8040_evp_summary.xlsx
+++ b/database/event/8040/event_8040_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.5929</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6.5295</v>
       </c>
       <c r="D2" t="n">
         <v>3.8579</v>
@@ -545,7 +545,7 @@
         <v>9.746</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6.0075</v>
       </c>
       <c r="D3" t="n">
         <v>3.5158</v>
@@ -591,7 +591,7 @@
         <v>8.9579</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5.5217</v>
       </c>
       <c r="D4" t="n">
         <v>3.1974</v>
@@ -637,7 +637,7 @@
         <v>8.9535</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5.519</v>
       </c>
       <c r="D5" t="n">
         <v>3.1957</v>
@@ -683,7 +683,7 @@
         <v>7.8414</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.8335</v>
       </c>
       <c r="D6" t="n">
         <v>2.7464</v>
@@ -729,7 +729,7 @@
         <v>7.4717</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4.6056</v>
       </c>
       <c r="D7" t="n">
         <v>2.597</v>
@@ -775,7 +775,7 @@
         <v>7.4536</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>4.5944</v>
       </c>
       <c r="D8" t="n">
         <v>2.5897</v>
@@ -821,7 +821,7 @@
         <v>6.4442</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.9722</v>
       </c>
       <c r="D9" t="n">
         <v>2.182</v>
@@ -867,7 +867,7 @@
         <v>5.8464</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3.6037</v>
       </c>
       <c r="D10" t="n">
         <v>1.9405</v>
@@ -913,7 +913,7 @@
         <v>5.7256</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3.5293</v>
       </c>
       <c r="D11" t="n">
         <v>1.8917</v>
@@ -959,7 +959,7 @@
         <v>5.6465</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>3.4805</v>
       </c>
       <c r="D12" t="n">
         <v>1.8597</v>
@@ -1005,7 +1005,7 @@
         <v>5.3028</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3.2687</v>
       </c>
       <c r="D13" t="n">
         <v>1.7209</v>
@@ -1051,7 +1051,7 @@
         <v>5.1067</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3.1478</v>
       </c>
       <c r="D14" t="n">
         <v>1.6416</v>
@@ -1097,7 +1097,7 @@
         <v>4.6246</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.8506</v>
       </c>
       <c r="D15" t="n">
         <v>1.4469</v>
@@ -1143,7 +1143,7 @@
         <v>4.1127</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.5351</v>
       </c>
       <c r="D16" t="n">
         <v>1.2401</v>
@@ -1189,7 +1189,7 @@
         <v>4.0517</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2.4975</v>
       </c>
       <c r="D17" t="n">
         <v>1.2154</v>
@@ -1235,7 +1235,7 @@
         <v>4.0088</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2.471</v>
       </c>
       <c r="D18" t="n">
         <v>1.1981</v>
@@ -1281,7 +1281,7 @@
         <v>3.8865</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2.3957</v>
       </c>
       <c r="D19" t="n">
         <v>1.1487</v>
@@ -1327,7 +1327,7 @@
         <v>3.7432</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.3073</v>
       </c>
       <c r="D20" t="n">
         <v>1.0908</v>
@@ -1373,7 +1373,7 @@
         <v>3.22</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.9848</v>
       </c>
       <c r="D21" t="n">
         <v>0.8794</v>
@@ -1419,7 +1419,7 @@
         <v>2.929</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.8054</v>
       </c>
       <c r="D22" t="n">
         <v>0.7619</v>
@@ -1465,7 +1465,7 @@
         <v>2.7438</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.6913</v>
       </c>
       <c r="D23" t="n">
         <v>0.6871</v>
@@ -1511,7 +1511,7 @@
         <v>2.7281</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.6816</v>
       </c>
       <c r="D24" t="n">
         <v>0.6807</v>
@@ -1557,7 +1557,7 @@
         <v>2.6709</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.6464</v>
       </c>
       <c r="D25" t="n">
         <v>0.6576</v>
@@ -1603,7 +1603,7 @@
         <v>2.6057</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.6062</v>
       </c>
       <c r="D26" t="n">
         <v>0.6313</v>
@@ -1649,7 +1649,7 @@
         <v>2.6002</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.6028</v>
       </c>
       <c r="D27" t="n">
         <v>0.6291</v>
@@ -1695,7 +1695,7 @@
         <v>2.2953</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.4148</v>
       </c>
       <c r="D28" t="n">
         <v>0.5059</v>
@@ -1741,7 +1741,7 @@
         <v>2.1157</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.3041</v>
       </c>
       <c r="D29" t="n">
         <v>0.4333</v>
@@ -1787,7 +1787,7 @@
         <v>1.8902</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.1651</v>
       </c>
       <c r="D30" t="n">
         <v>0.3422</v>
@@ -1833,7 +1833,7 @@
         <v>1.6981</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1.0467</v>
       </c>
       <c r="D31" t="n">
         <v>0.2646</v>
@@ -1879,7 +1879,7 @@
         <v>1.5497</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.9552</v>
       </c>
       <c r="D32" t="n">
         <v>0.2047</v>
@@ -1925,7 +1925,7 @@
         <v>1.5101</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.9308</v>
       </c>
       <c r="D33" t="n">
         <v>0.1887</v>
@@ -1971,7 +1971,7 @@
         <v>1.3707</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.8449</v>
       </c>
       <c r="D34" t="n">
         <v>0.1324</v>
@@ -2017,7 +2017,7 @@
         <v>0.9748</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6009</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0276</v>
@@ -2063,7 +2063,7 @@
         <v>0.9264</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="D36" t="n">
         <v>-0.0471</v>
@@ -2109,7 +2109,7 @@
         <v>0.8082</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4982</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0949</v>
@@ -2155,7 +2155,7 @@
         <v>0.7936</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4892</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1008</v>
@@ -2201,7 +2201,7 @@
         <v>0.7054</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4348</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1364</v>
@@ -2247,7 +2247,7 @@
         <v>0.6183999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.3812</v>
       </c>
       <c r="D40" t="n">
         <v>-0.1715</v>
@@ -2293,7 +2293,7 @@
         <v>0.5893</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.3632</v>
       </c>
       <c r="D41" t="n">
         <v>-0.1833</v>
@@ -2339,7 +2339,7 @@
         <v>0.5201</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.3206</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2113</v>
@@ -2385,7 +2385,7 @@
         <v>0.4751</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2929</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2294</v>
@@ -2431,7 +2431,7 @@
         <v>0.4651</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2867</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2335</v>
@@ -2477,7 +2477,7 @@
         <v>0.3296</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2032</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2882</v>
@@ -2523,7 +2523,7 @@
         <v>0.2364</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1457</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3259</v>
@@ -2569,7 +2569,7 @@
         <v>0.2303</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3283</v>
@@ -2615,7 +2615,7 @@
         <v>0.1872</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1154</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3457</v>
@@ -2661,7 +2661,7 @@
         <v>0.1724</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1063</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3517</v>
@@ -2707,7 +2707,7 @@
         <v>0.1279</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0788</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3697</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0311</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0192</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4339</v>
@@ -2799,7 +2799,7 @@
         <v>-0.08160000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0503</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4543</v>
@@ -2845,7 +2845,7 @@
         <v>-0.2916</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1797</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5392</v>
@@ -2891,7 +2891,7 @@
         <v>-0.3595</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.2216</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5666</v>
@@ -2937,7 +2937,7 @@
         <v>-0.4504</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.2776</v>
       </c>
       <c r="D55" t="n">
         <v>-0.6032999999999999</v>
@@ -2983,7 +2983,7 @@
         <v>-0.4578</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.2822</v>
       </c>
       <c r="D56" t="n">
         <v>-0.6063</v>
@@ -3029,7 +3029,7 @@
         <v>-0.505</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.3113</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6254</v>
@@ -3075,7 +3075,7 @@
         <v>-0.8152</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="D58" t="n">
         <v>-0.7507</v>
@@ -3121,7 +3121,7 @@
         <v>-0.8917</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.5496</v>
       </c>
       <c r="D59" t="n">
         <v>-0.7816</v>
@@ -3167,7 +3167,7 @@
         <v>-0.9643</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.5944</v>
       </c>
       <c r="D60" t="n">
         <v>-0.8109</v>
@@ -3213,7 +3213,7 @@
         <v>-1.0645</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.6562</v>
       </c>
       <c r="D61" t="n">
         <v>-0.8514</v>
@@ -3259,7 +3259,7 @@
         <v>-1.2196</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.7518</v>
       </c>
       <c r="D62" t="n">
         <v>-0.9141</v>
@@ -3305,7 +3305,7 @@
         <v>-1.2196</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.7518</v>
       </c>
       <c r="D63" t="n">
         <v>-0.9141</v>
@@ -3351,7 +3351,7 @@
         <v>-1.2575</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.7751</v>
       </c>
       <c r="D64" t="n">
         <v>-0.9294</v>
@@ -3397,7 +3397,7 @@
         <v>-1.3179</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.8124</v>
       </c>
       <c r="D65" t="n">
         <v>-0.9538</v>
@@ -3443,7 +3443,7 @@
         <v>-1.3594</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.8379</v>
       </c>
       <c r="D66" t="n">
         <v>-0.9705</v>
@@ -3489,7 +3489,7 @@
         <v>-1.4189</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.8746</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9946</v>
@@ -3535,7 +3535,7 @@
         <v>-1.4806</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.9126</v>
       </c>
       <c r="D68" t="n">
         <v>-1.0195</v>
@@ -3581,7 +3581,7 @@
         <v>-1.5365</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="D69" t="n">
         <v>-1.0421</v>
@@ -3627,7 +3627,7 @@
         <v>-1.5608</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.9621</v>
       </c>
       <c r="D70" t="n">
         <v>-1.0519</v>
@@ -3673,7 +3673,7 @@
         <v>-1.7009</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-1.0484</v>
       </c>
       <c r="D71" t="n">
         <v>-1.1085</v>
@@ -3719,7 +3719,7 @@
         <v>-1.7576</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-1.0834</v>
       </c>
       <c r="D72" t="n">
         <v>-1.1314</v>
@@ -3765,7 +3765,7 @@
         <v>-2.1241</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-1.3093</v>
       </c>
       <c r="D73" t="n">
         <v>-1.2795</v>
@@ -3811,7 +3811,7 @@
         <v>-2.1484</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.3243</v>
       </c>
       <c r="D74" t="n">
         <v>-1.2893</v>
@@ -3857,7 +3857,7 @@
         <v>-2.254</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.3894</v>
       </c>
       <c r="D75" t="n">
         <v>-1.3319</v>
@@ -3903,7 +3903,7 @@
         <v>-2.7696</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.7072</v>
       </c>
       <c r="D76" t="n">
         <v>-1.5402</v>
@@ -3949,7 +3949,7 @@
         <v>-2.7886</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.7189</v>
       </c>
       <c r="D77" t="n">
         <v>-1.5479</v>
@@ -3995,7 +3995,7 @@
         <v>-2.945</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.8153</v>
       </c>
       <c r="D78" t="n">
         <v>-1.6111</v>
@@ -4041,7 +4041,7 @@
         <v>-3.1417</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.9366</v>
       </c>
       <c r="D79" t="n">
         <v>-1.6905</v>
@@ -4087,7 +4087,7 @@
         <v>-4.1777</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.5751</v>
       </c>
       <c r="D80" t="n">
         <v>-2.1091</v>
@@ -4133,7 +4133,7 @@
         <v>-4.4645</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.7519</v>
       </c>
       <c r="D81" t="n">
         <v>-2.2249</v>

--- a/database/event/8040/event_8040_evp_summary.xlsx
+++ b/database/event/8040/event_8040_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>6.5295</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8579</v>
+        <v>3.7763</v>
       </c>
       <c r="E2" t="n">
         <v>10.5929</v>
@@ -548,7 +548,7 @@
         <v>6.0075</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5158</v>
+        <v>3.4389</v>
       </c>
       <c r="E3" t="n">
         <v>9.746</v>
@@ -594,7 +594,7 @@
         <v>5.5217</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1974</v>
+        <v>3.1249</v>
       </c>
       <c r="E4" t="n">
         <v>8.9579</v>
@@ -640,7 +640,7 @@
         <v>5.519</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1957</v>
+        <v>3.1232</v>
       </c>
       <c r="E5" t="n">
         <v>8.9535</v>
@@ -686,7 +686,7 @@
         <v>4.8335</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7464</v>
+        <v>2.6801</v>
       </c>
       <c r="E6" t="n">
         <v>7.8414</v>
@@ -732,7 +732,7 @@
         <v>4.6056</v>
       </c>
       <c r="D7" t="n">
-        <v>2.597</v>
+        <v>2.5328</v>
       </c>
       <c r="E7" t="n">
         <v>7.4717</v>
@@ -778,7 +778,7 @@
         <v>4.5944</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5897</v>
+        <v>2.5256</v>
       </c>
       <c r="E8" t="n">
         <v>7.4536</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.4442</v>
+        <v>6.433</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9722</v>
+        <v>3.9653</v>
       </c>
       <c r="D9" t="n">
-        <v>2.182</v>
+        <v>2.119</v>
       </c>
       <c r="E9" t="n">
-        <v>6.4442</v>
+        <v>6.433</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4615</v>
+        <v>4.4503</v>
       </c>
       <c r="G9" t="n">
         <v>1.9827</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6925</v>
+        <v>4.675</v>
       </c>
       <c r="I9" t="n">
         <v>4.7144</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.8464</v>
+        <v>5.8353</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6037</v>
+        <v>3.5969</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9405</v>
+        <v>1.8809</v>
       </c>
       <c r="E10" t="n">
-        <v>5.8464</v>
+        <v>5.8353</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4543</v>
+        <v>4.4432</v>
       </c>
       <c r="G10" t="n">
         <v>1.3921</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6813</v>
+        <v>4.6638</v>
       </c>
       <c r="I10" t="n">
         <v>4.7031</v>
@@ -916,7 +916,7 @@
         <v>3.5293</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8917</v>
+        <v>1.8372</v>
       </c>
       <c r="E11" t="n">
         <v>5.7256</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6465</v>
+        <v>5.6306</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4805</v>
+        <v>3.4707</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8597</v>
+        <v>1.7993</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6465</v>
+        <v>5.6306</v>
       </c>
       <c r="F12" t="n">
-        <v>5.7372</v>
+        <v>5.7213</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0907</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6928</v>
+        <v>6.6679</v>
       </c>
       <c r="I12" t="n">
         <v>6.724</v>
@@ -1008,7 +1008,7 @@
         <v>3.2687</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7209</v>
+        <v>1.6687</v>
       </c>
       <c r="E13" t="n">
         <v>5.3028</v>
@@ -1054,7 +1054,7 @@
         <v>3.1478</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6416</v>
+        <v>1.5906</v>
       </c>
       <c r="E14" t="n">
         <v>5.1067</v>
@@ -1100,7 +1100,7 @@
         <v>2.8506</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4469</v>
+        <v>1.3985</v>
       </c>
       <c r="E15" t="n">
         <v>4.6246</v>
@@ -1146,7 +1146,7 @@
         <v>2.5351</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2401</v>
+        <v>1.1946</v>
       </c>
       <c r="E16" t="n">
         <v>4.1127</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.0517</v>
+        <v>4.0414</v>
       </c>
       <c r="C17" t="n">
-        <v>2.4975</v>
+        <v>2.4911</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2154</v>
+        <v>1.1662</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0517</v>
+        <v>4.0414</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2378</v>
+        <v>4.2275</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1861</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3419</v>
+        <v>4.3257</v>
       </c>
       <c r="I17" t="n">
         <v>4.3621</v>
@@ -1238,7 +1238,7 @@
         <v>2.471</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1981</v>
+        <v>1.1532</v>
       </c>
       <c r="E18" t="n">
         <v>4.0088</v>
@@ -1284,7 +1284,7 @@
         <v>2.3957</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1487</v>
+        <v>1.1045</v>
       </c>
       <c r="E19" t="n">
         <v>3.8865</v>
@@ -1330,7 +1330,7 @@
         <v>2.3073</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0908</v>
+        <v>1.0474</v>
       </c>
       <c r="E20" t="n">
         <v>3.7432</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.22</v>
+        <v>3.2102</v>
       </c>
       <c r="C21" t="n">
-        <v>1.9848</v>
+        <v>1.9788</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8794</v>
+        <v>0.835</v>
       </c>
       <c r="E21" t="n">
-        <v>3.22</v>
+        <v>3.2102</v>
       </c>
       <c r="F21" t="n">
-        <v>4.0859</v>
+        <v>4.0761</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8659</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1036</v>
+        <v>4.0883</v>
       </c>
       <c r="I21" t="n">
         <v>4.1227</v>
@@ -1422,7 +1422,7 @@
         <v>1.8054</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7619</v>
+        <v>0.723</v>
       </c>
       <c r="E22" t="n">
         <v>2.929</v>
@@ -1468,7 +1468,7 @@
         <v>1.6913</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6871</v>
+        <v>0.6492</v>
       </c>
       <c r="E23" t="n">
         <v>2.7438</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7281</v>
+        <v>2.7189</v>
       </c>
       <c r="C24" t="n">
-        <v>1.6816</v>
+        <v>1.6759</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6807</v>
+        <v>0.6393</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7281</v>
+        <v>2.7189</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4584</v>
+        <v>2.4492</v>
       </c>
       <c r="G24" t="n">
         <v>0.2697</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4584</v>
+        <v>2.4492</v>
       </c>
       <c r="I24" t="n">
         <v>2.4698</v>
@@ -1560,7 +1560,7 @@
         <v>1.6464</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6576</v>
+        <v>0.6202</v>
       </c>
       <c r="E25" t="n">
         <v>2.6709</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6057</v>
+        <v>2.6002</v>
       </c>
       <c r="C26" t="n">
-        <v>1.6062</v>
+        <v>1.6028</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6313</v>
+        <v>0.592</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6057</v>
+        <v>2.6002</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5168</v>
+        <v>2.806</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0889</v>
+        <v>-0.2058</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5168</v>
+        <v>2.806</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5239</v>
+        <v>2.806</v>
       </c>
       <c r="J26" t="n">
-        <v>1.0889</v>
+        <v>-0.2058</v>
       </c>
       <c r="K26" t="n">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="L26" t="n">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6128</v>
+        <v>2.6002</v>
       </c>
       <c r="N26" t="n">
-        <v>336</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.6002</v>
+        <v>2.6</v>
       </c>
       <c r="C27" t="n">
-        <v>1.6028</v>
+        <v>1.6026</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6291</v>
+        <v>0.5919</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6002</v>
+        <v>2.6</v>
       </c>
       <c r="F27" t="n">
-        <v>2.806</v>
+        <v>1.5111</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2058</v>
+        <v>1.0889</v>
       </c>
       <c r="H27" t="n">
-        <v>2.806</v>
+        <v>1.5111</v>
       </c>
       <c r="I27" t="n">
-        <v>2.806</v>
+        <v>1.5239</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2058</v>
+        <v>1.0889</v>
       </c>
       <c r="K27" t="n">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>2.6002</v>
+        <v>2.6128</v>
       </c>
       <c r="N27" t="n">
-        <v>180</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28">
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2953</v>
+        <v>2.2921</v>
       </c>
       <c r="C28" t="n">
-        <v>1.4148</v>
+        <v>1.4129</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5059</v>
+        <v>0.4693</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2953</v>
+        <v>2.2921</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8471</v>
       </c>
       <c r="G28" t="n">
         <v>1.445</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8471</v>
       </c>
       <c r="I28" t="n">
         <v>0.8542999999999999</v>
@@ -1744,7 +1744,7 @@
         <v>1.3041</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4333</v>
+        <v>0.399</v>
       </c>
       <c r="E29" t="n">
         <v>2.1157</v>
@@ -1790,7 +1790,7 @@
         <v>1.1651</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3422</v>
+        <v>0.3091</v>
       </c>
       <c r="E30" t="n">
         <v>1.8902</v>
@@ -1836,7 +1836,7 @@
         <v>1.0467</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2646</v>
+        <v>0.2326</v>
       </c>
       <c r="E31" t="n">
         <v>1.6981</v>
@@ -1882,7 +1882,7 @@
         <v>0.9552</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2047</v>
+        <v>0.1735</v>
       </c>
       <c r="E32" t="n">
         <v>1.5497</v>
@@ -1928,7 +1928,7 @@
         <v>0.9308</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1887</v>
+        <v>0.1577</v>
       </c>
       <c r="E33" t="n">
         <v>1.5101</v>
@@ -1974,7 +1974,7 @@
         <v>0.8449</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1324</v>
+        <v>0.1022</v>
       </c>
       <c r="E34" t="n">
         <v>1.3707</v>
@@ -2020,7 +2020,7 @@
         <v>0.6009</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0276</v>
+        <v>-0.0555</v>
       </c>
       <c r="E35" t="n">
         <v>0.9748</v>
@@ -2066,7 +2066,7 @@
         <v>0.571</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0471</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="E36" t="n">
         <v>0.9264</v>
@@ -2112,7 +2112,7 @@
         <v>0.4982</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0949</v>
+        <v>-0.1219</v>
       </c>
       <c r="E37" t="n">
         <v>0.8082</v>
@@ -2158,7 +2158,7 @@
         <v>0.4892</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1008</v>
+        <v>-0.1277</v>
       </c>
       <c r="E38" t="n">
         <v>0.7936</v>
@@ -2204,7 +2204,7 @@
         <v>0.4348</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1364</v>
+        <v>-0.1629</v>
       </c>
       <c r="E39" t="n">
         <v>0.7054</v>
@@ -2250,7 +2250,7 @@
         <v>0.3812</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1715</v>
+        <v>-0.1975</v>
       </c>
       <c r="E40" t="n">
         <v>0.6183999999999999</v>
@@ -2296,7 +2296,7 @@
         <v>0.3632</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1833</v>
+        <v>-0.2091</v>
       </c>
       <c r="E41" t="n">
         <v>0.5893</v>
@@ -2342,7 +2342,7 @@
         <v>0.3206</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2113</v>
+        <v>-0.2367</v>
       </c>
       <c r="E42" t="n">
         <v>0.5201</v>
@@ -2388,7 +2388,7 @@
         <v>0.2929</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2294</v>
+        <v>-0.2546</v>
       </c>
       <c r="E43" t="n">
         <v>0.4751</v>
@@ -2434,7 +2434,7 @@
         <v>0.2867</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2335</v>
+        <v>-0.2586</v>
       </c>
       <c r="E44" t="n">
         <v>0.4651</v>
@@ -2480,7 +2480,7 @@
         <v>0.2032</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2882</v>
+        <v>-0.3126</v>
       </c>
       <c r="E45" t="n">
         <v>0.3296</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2364</v>
+        <v>0.2318</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1457</v>
+        <v>0.1429</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3259</v>
+        <v>-0.3516</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2364</v>
+        <v>0.2318</v>
       </c>
       <c r="F46" t="n">
-        <v>1.2364</v>
+        <v>1.2318</v>
       </c>
       <c r="G46" t="n">
         <v>-1</v>
       </c>
       <c r="H46" t="n">
-        <v>1.2364</v>
+        <v>1.2318</v>
       </c>
       <c r="I46" t="n">
         <v>1.2422</v>
@@ -2572,7 +2572,7 @@
         <v>0.142</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3283</v>
+        <v>-0.3522</v>
       </c>
       <c r="E47" t="n">
         <v>0.2303</v>
@@ -2618,7 +2618,7 @@
         <v>0.1154</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3457</v>
+        <v>-0.3693</v>
       </c>
       <c r="E48" t="n">
         <v>0.1872</v>
@@ -2664,7 +2664,7 @@
         <v>0.1063</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3517</v>
+        <v>-0.3752</v>
       </c>
       <c r="E49" t="n">
         <v>0.1724</v>
@@ -2710,7 +2710,7 @@
         <v>0.0788</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3697</v>
+        <v>-0.393</v>
       </c>
       <c r="E50" t="n">
         <v>0.1279</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0192</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4339</v>
+        <v>-0.4563</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0311</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0503</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4543</v>
+        <v>-0.4764</v>
       </c>
       <c r="E52" t="n">
         <v>-0.08160000000000001</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1797</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5392</v>
+        <v>-0.5601</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2916</v>
@@ -2894,7 +2894,7 @@
         <v>-0.2216</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5666</v>
+        <v>-0.5871</v>
       </c>
       <c r="E54" t="n">
         <v>-0.3595</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2776</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.6233</v>
       </c>
       <c r="E55" t="n">
         <v>-0.4504</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2822</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6063</v>
+        <v>-0.6263</v>
       </c>
       <c r="E56" t="n">
         <v>-0.4578</v>
@@ -3032,7 +3032,7 @@
         <v>-0.3113</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6254</v>
+        <v>-0.6451</v>
       </c>
       <c r="E57" t="n">
         <v>-0.505</v>
@@ -3078,7 +3078,7 @@
         <v>-0.5024999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7507</v>
+        <v>-0.7687</v>
       </c>
       <c r="E58" t="n">
         <v>-0.8152</v>
@@ -3124,7 +3124,7 @@
         <v>-0.5496</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7816</v>
+        <v>-0.7992</v>
       </c>
       <c r="E59" t="n">
         <v>-0.8917</v>
@@ -3170,7 +3170,7 @@
         <v>-0.5944</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.8109</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="E60" t="n">
         <v>-0.9643</v>
@@ -3216,7 +3216,7 @@
         <v>-0.6562</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8514</v>
+        <v>-0.868</v>
       </c>
       <c r="E61" t="n">
         <v>-1.0645</v>
@@ -3262,7 +3262,7 @@
         <v>-0.7518</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.9141</v>
+        <v>-0.9298</v>
       </c>
       <c r="E62" t="n">
         <v>-1.2196</v>
@@ -3308,7 +3308,7 @@
         <v>-0.7518</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.9141</v>
+        <v>-0.9298</v>
       </c>
       <c r="E63" t="n">
         <v>-1.2196</v>
@@ -3354,7 +3354,7 @@
         <v>-0.7751</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9294</v>
+        <v>-0.9449</v>
       </c>
       <c r="E64" t="n">
         <v>-1.2575</v>
@@ -3400,7 +3400,7 @@
         <v>-0.8124</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9538</v>
+        <v>-0.969</v>
       </c>
       <c r="E65" t="n">
         <v>-1.3179</v>
@@ -3446,7 +3446,7 @@
         <v>-0.8379</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9705</v>
+        <v>-0.9855</v>
       </c>
       <c r="E66" t="n">
         <v>-1.3594</v>
@@ -3492,7 +3492,7 @@
         <v>-0.8746</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9946</v>
+        <v>-1.0092</v>
       </c>
       <c r="E67" t="n">
         <v>-1.4189</v>
@@ -3538,7 +3538,7 @@
         <v>-0.9126</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0195</v>
+        <v>-1.0338</v>
       </c>
       <c r="E68" t="n">
         <v>-1.4806</v>
@@ -3584,7 +3584,7 @@
         <v>-0.9471000000000001</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0421</v>
+        <v>-1.0561</v>
       </c>
       <c r="E69" t="n">
         <v>-1.5365</v>
@@ -3630,7 +3630,7 @@
         <v>-0.9621</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0519</v>
+        <v>-1.0657</v>
       </c>
       <c r="E70" t="n">
         <v>-1.5608</v>
@@ -3676,7 +3676,7 @@
         <v>-1.0484</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1085</v>
+        <v>-1.1215</v>
       </c>
       <c r="E71" t="n">
         <v>-1.7009</v>
@@ -3722,7 +3722,7 @@
         <v>-1.0834</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1314</v>
+        <v>-1.1441</v>
       </c>
       <c r="E72" t="n">
         <v>-1.7576</v>
@@ -3768,7 +3768,7 @@
         <v>-1.3093</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2795</v>
+        <v>-1.2902</v>
       </c>
       <c r="E73" t="n">
         <v>-2.1241</v>
@@ -3814,7 +3814,7 @@
         <v>-1.3243</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2893</v>
+        <v>-1.2998</v>
       </c>
       <c r="E74" t="n">
         <v>-2.1484</v>
@@ -3860,7 +3860,7 @@
         <v>-1.3894</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3319</v>
+        <v>-1.3419</v>
       </c>
       <c r="E75" t="n">
         <v>-2.254</v>
@@ -3906,7 +3906,7 @@
         <v>-1.7072</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5402</v>
+        <v>-1.5473</v>
       </c>
       <c r="E76" t="n">
         <v>-2.7696</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.7886</v>
+        <v>-2.7784</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.7189</v>
+        <v>-1.7126</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5479</v>
+        <v>-1.5508</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.7886</v>
+        <v>-2.7784</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.74</v>
+        <v>-2.7298</v>
       </c>
       <c r="G77" t="n">
         <v>-0.0486</v>
       </c>
       <c r="H77" t="n">
-        <v>-2.74</v>
+        <v>-2.7298</v>
       </c>
       <c r="I77" t="n">
         <v>-2.7528</v>
@@ -3998,7 +3998,7 @@
         <v>-1.8153</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.6111</v>
+        <v>-1.6172</v>
       </c>
       <c r="E78" t="n">
         <v>-2.945</v>
@@ -4044,7 +4044,7 @@
         <v>-1.9366</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6905</v>
+        <v>-1.6956</v>
       </c>
       <c r="E79" t="n">
         <v>-3.1417</v>
@@ -4090,7 +4090,7 @@
         <v>-2.5751</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.1091</v>
+        <v>-2.1083</v>
       </c>
       <c r="E80" t="n">
         <v>-4.1777</v>
@@ -4136,7 +4136,7 @@
         <v>-2.7519</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2249</v>
+        <v>-2.2226</v>
       </c>
       <c r="E81" t="n">
         <v>-4.4645</v>

--- a/database/event/8040/event_8040_evp_summary.xlsx
+++ b/database/event/8040/event_8040_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.6059</v>
+        <v>9.9468</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9211</v>
+        <v>6.1312</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7486</v>
+        <v>3.8292</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6059</v>
+        <v>9.9468</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1879</v>
+        <v>4.1868</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4181</v>
+        <v>5.4186</v>
       </c>
       <c r="H2" t="n">
-        <v>6.441</v>
+        <v>6.4386</v>
       </c>
       <c r="I2" t="n">
-        <v>6.441</v>
+        <v>6.4386</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4181</v>
+        <v>5.4186</v>
       </c>
       <c r="K2" t="n">
         <v>143</v>
@@ -529,7 +529,7 @@
         <v>183</v>
       </c>
       <c r="M2" t="n">
-        <v>11.8591</v>
+        <v>11.8572</v>
       </c>
       <c r="N2" t="n">
         <v>326</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.276300000000001</v>
+        <v>9.517899999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>5.7179</v>
+        <v>5.8669</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5986</v>
+        <v>3.6376</v>
       </c>
       <c r="E3" t="n">
-        <v>9.276300000000001</v>
+        <v>9.517899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7488</v>
+        <v>3.7428</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5275</v>
+        <v>5.5279</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4801</v>
+        <v>5.4668</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4801</v>
+        <v>5.4668</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5275</v>
+        <v>5.5279</v>
       </c>
       <c r="K3" t="n">
         <v>156</v>
@@ -575,7 +575,7 @@
         <v>210</v>
       </c>
       <c r="M3" t="n">
-        <v>11.0076</v>
+        <v>10.9947</v>
       </c>
       <c r="N3" t="n">
         <v>366</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.760999999999999</v>
+        <v>8.8775</v>
       </c>
       <c r="C4" t="n">
-        <v>5.4003</v>
+        <v>5.4721</v>
       </c>
       <c r="D4" t="n">
-        <v>3.364</v>
+        <v>3.3516</v>
       </c>
       <c r="E4" t="n">
-        <v>8.760999999999999</v>
+        <v>8.8775</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1168</v>
+        <v>3.1165</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6442</v>
+        <v>5.6299</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0968</v>
+        <v>4.0962</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0968</v>
+        <v>4.0962</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6442</v>
+        <v>5.6299</v>
       </c>
       <c r="K4" t="n">
         <v>156</v>
@@ -621,7 +621,7 @@
         <v>210</v>
       </c>
       <c r="M4" t="n">
-        <v>9.741</v>
+        <v>9.726099999999999</v>
       </c>
       <c r="N4" t="n">
         <v>366</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.8671</v>
+        <v>8.1485</v>
       </c>
       <c r="C5" t="n">
-        <v>4.8493</v>
+        <v>5.0228</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9571</v>
+        <v>3.0259</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8671</v>
+        <v>8.1485</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4696</v>
+        <v>3.4646</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3975</v>
+        <v>4.3967</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8689</v>
+        <v>4.858</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8689</v>
+        <v>4.858</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3975</v>
+        <v>4.3967</v>
       </c>
       <c r="K5" t="n">
         <v>227</v>
@@ -667,7 +667,7 @@
         <v>125</v>
       </c>
       <c r="M5" t="n">
-        <v>9.266400000000001</v>
+        <v>9.2547</v>
       </c>
       <c r="N5" t="n">
         <v>352</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.0452</v>
+        <v>7.2389</v>
       </c>
       <c r="C6" t="n">
-        <v>4.3427</v>
+        <v>4.4621</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5829</v>
+        <v>2.6196</v>
       </c>
       <c r="E6" t="n">
-        <v>7.0452</v>
+        <v>7.2389</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1521</v>
+        <v>4.1463</v>
       </c>
       <c r="G6" t="n">
-        <v>2.893</v>
+        <v>2.9209</v>
       </c>
       <c r="H6" t="n">
-        <v>6.3628</v>
+        <v>6.35</v>
       </c>
       <c r="I6" t="n">
-        <v>6.3628</v>
+        <v>6.35</v>
       </c>
       <c r="J6" t="n">
-        <v>2.893</v>
+        <v>2.9209</v>
       </c>
       <c r="K6" t="n">
         <v>227</v>
@@ -713,7 +713,7 @@
         <v>125</v>
       </c>
       <c r="M6" t="n">
-        <v>9.255800000000001</v>
+        <v>9.270899999999999</v>
       </c>
       <c r="N6" t="n">
         <v>352</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.8124</v>
+        <v>6.9064</v>
       </c>
       <c r="C7" t="n">
-        <v>4.1992</v>
+        <v>4.2571</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4769</v>
+        <v>2.4711</v>
       </c>
       <c r="E7" t="n">
-        <v>6.8124</v>
+        <v>6.9064</v>
       </c>
       <c r="F7" t="n">
-        <v>4.043</v>
+        <v>4.0748</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7694</v>
+        <v>2.7697</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1239</v>
+        <v>6.1936</v>
       </c>
       <c r="I7" t="n">
-        <v>6.1239</v>
+        <v>6.1936</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7694</v>
+        <v>2.7697</v>
       </c>
       <c r="K7" t="n">
         <v>156</v>
@@ -759,7 +759,7 @@
         <v>210</v>
       </c>
       <c r="M7" t="n">
-        <v>8.8933</v>
+        <v>8.9633</v>
       </c>
       <c r="N7" t="n">
         <v>366</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.4862</v>
+        <v>6.5552</v>
       </c>
       <c r="C8" t="n">
-        <v>3.9981</v>
+        <v>4.0406</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3284</v>
+        <v>2.3142</v>
       </c>
       <c r="E8" t="n">
-        <v>6.4862</v>
+        <v>6.5552</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1231</v>
+        <v>4.1293</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3631</v>
+        <v>2.3634</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2992</v>
+        <v>6.3127</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2992</v>
+        <v>6.3127</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3631</v>
+        <v>2.3634</v>
       </c>
       <c r="K8" t="n">
         <v>156</v>
@@ -805,7 +805,7 @@
         <v>210</v>
       </c>
       <c r="M8" t="n">
-        <v>8.6623</v>
+        <v>8.6761</v>
       </c>
       <c r="N8" t="n">
         <v>366</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8482</v>
+        <v>6.0052</v>
       </c>
       <c r="C9" t="n">
-        <v>3.6048</v>
+        <v>3.7016</v>
       </c>
       <c r="D9" t="n">
-        <v>2.038</v>
+        <v>2.0686</v>
       </c>
       <c r="E9" t="n">
-        <v>5.8482</v>
+        <v>6.0052</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8592</v>
+        <v>3.8641</v>
       </c>
       <c r="G9" t="n">
-        <v>1.989</v>
+        <v>1.9898</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7216</v>
+        <v>5.7323</v>
       </c>
       <c r="I9" t="n">
-        <v>5.869</v>
+        <v>5.88</v>
       </c>
       <c r="J9" t="n">
-        <v>1.989</v>
+        <v>1.9898</v>
       </c>
       <c r="K9" t="n">
         <v>245</v>
@@ -851,7 +851,7 @@
         <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>7.858</v>
+        <v>7.8698</v>
       </c>
       <c r="N9" t="n">
         <v>313</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.1821</v>
+        <v>5.405</v>
       </c>
       <c r="C10" t="n">
-        <v>3.1943</v>
+        <v>3.3317</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7348</v>
+        <v>1.8005</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1821</v>
+        <v>5.405</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9201</v>
+        <v>4.9255</v>
       </c>
       <c r="G10" t="n">
-        <v>0.262</v>
+        <v>0.2601</v>
       </c>
       <c r="H10" t="n">
-        <v>8.0435</v>
+        <v>8.055400000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>8.2508</v>
+        <v>8.263</v>
       </c>
       <c r="J10" t="n">
-        <v>0.262</v>
+        <v>0.2601</v>
       </c>
       <c r="K10" t="n">
         <v>219</v>
@@ -897,7 +897,7 @@
         <v>117</v>
       </c>
       <c r="M10" t="n">
-        <v>8.5128</v>
+        <v>8.523099999999999</v>
       </c>
       <c r="N10" t="n">
         <v>336</v>
@@ -906,231 +906,231 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.1236</v>
+        <v>5.3216</v>
       </c>
       <c r="C11" t="n">
-        <v>3.1582</v>
+        <v>3.2803</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7082</v>
+        <v>1.7632</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1236</v>
+        <v>5.3216</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5371</v>
+        <v>4.8114</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5865</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8279</v>
+        <v>7.8058</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8279</v>
+        <v>7.8058</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5865</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="L11" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.414400000000001</v>
+        <v>7.8058</v>
       </c>
       <c r="N11" t="n">
-        <v>326</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.8113</v>
+        <v>5.1844</v>
       </c>
       <c r="C12" t="n">
-        <v>2.9657</v>
+        <v>3.1957</v>
       </c>
       <c r="D12" t="n">
-        <v>1.566</v>
+        <v>1.7019</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8113</v>
+        <v>5.1844</v>
       </c>
       <c r="F12" t="n">
-        <v>4.8113</v>
+        <v>2.5367</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.5868</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8055</v>
+        <v>2.8272</v>
       </c>
       <c r="I12" t="n">
-        <v>7.8055</v>
+        <v>2.8272</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.5868</v>
       </c>
       <c r="K12" t="n">
-        <v>274</v>
+        <v>143</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M12" t="n">
-        <v>7.8055</v>
+        <v>5.414</v>
       </c>
       <c r="N12" t="n">
-        <v>274</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>donk</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.6912</v>
+        <v>4.9075</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8917</v>
+        <v>3.025</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5113</v>
+        <v>1.5783</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6912</v>
+        <v>4.9075</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5601</v>
+        <v>3.9064</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1311</v>
+        <v>0.5566</v>
       </c>
       <c r="H13" t="n">
-        <v>7.2556</v>
+        <v>5.8249</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2556</v>
+        <v>5.8249</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1311</v>
+        <v>0.5566</v>
       </c>
       <c r="K13" t="n">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="L13" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="M13" t="n">
-        <v>7.3867</v>
+        <v>6.381500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>243</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.5555</v>
+        <v>4.818</v>
       </c>
       <c r="C14" t="n">
-        <v>2.808</v>
+        <v>2.9698</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4496</v>
+        <v>1.5383</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5555</v>
+        <v>4.818</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3041</v>
+        <v>4.5602</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2514</v>
+        <v>0.1308</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5067</v>
+        <v>7.2558</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6228</v>
+        <v>7.2558</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2514</v>
+        <v>0.1308</v>
       </c>
       <c r="K14" t="n">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="L14" t="n">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="M14" t="n">
-        <v>5.8742</v>
+        <v>7.3866</v>
       </c>
       <c r="N14" t="n">
-        <v>336</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>donk</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.4689</v>
+        <v>4.6436</v>
       </c>
       <c r="C15" t="n">
-        <v>2.7546</v>
+        <v>2.8623</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4101</v>
+        <v>1.4604</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4689</v>
+        <v>4.6436</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9119</v>
+        <v>3.304</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5570000000000001</v>
+        <v>1.2776</v>
       </c>
       <c r="H15" t="n">
-        <v>5.837</v>
+        <v>4.5064</v>
       </c>
       <c r="I15" t="n">
-        <v>5.837</v>
+        <v>4.6225</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5570000000000001</v>
+        <v>1.2776</v>
       </c>
       <c r="K15" t="n">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="L15" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="M15" t="n">
-        <v>6.394</v>
+        <v>5.9001</v>
       </c>
       <c r="N15" t="n">
-        <v>180</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.2317</v>
+        <v>4.5517</v>
       </c>
       <c r="C16" t="n">
-        <v>2.6084</v>
+        <v>2.8057</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3022</v>
+        <v>1.4193</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2317</v>
+        <v>4.5517</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7023</v>
+        <v>3.6958</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5294</v>
+        <v>0.5401</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3783</v>
+        <v>5.364</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3783</v>
+        <v>5.364</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5294</v>
+        <v>0.5401</v>
       </c>
       <c r="K16" t="n">
         <v>181</v>
@@ -1173,7 +1173,7 @@
         <v>62</v>
       </c>
       <c r="M16" t="n">
-        <v>5.9077</v>
+        <v>5.9041</v>
       </c>
       <c r="N16" t="n">
         <v>243</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.2282</v>
+        <v>4.3834</v>
       </c>
       <c r="C17" t="n">
-        <v>2.6063</v>
+        <v>2.7019</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3006</v>
+        <v>1.3441</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2282</v>
+        <v>4.3834</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2415</v>
+        <v>4.2414</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0133</v>
+        <v>-0.0131</v>
       </c>
       <c r="H17" t="n">
-        <v>6.5583</v>
+        <v>6.5581</v>
       </c>
       <c r="I17" t="n">
-        <v>6.7273</v>
+        <v>6.7271</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0133</v>
+        <v>-0.0131</v>
       </c>
       <c r="K17" t="n">
         <v>245</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.0393</v>
+        <v>4.2307</v>
       </c>
       <c r="C18" t="n">
-        <v>2.4898</v>
+        <v>2.6078</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2146</v>
+        <v>1.2759</v>
       </c>
       <c r="E18" t="n">
-        <v>4.0393</v>
+        <v>4.2307</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7835</v>
+        <v>2.7796</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2558</v>
+        <v>1.2553</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3674</v>
+        <v>3.3588</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3674</v>
+        <v>3.3588</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2558</v>
+        <v>1.2553</v>
       </c>
       <c r="K18" t="n">
         <v>227</v>
@@ -1265,7 +1265,7 @@
         <v>125</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6232</v>
+        <v>4.614100000000001</v>
       </c>
       <c r="N18" t="n">
         <v>352</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.6393</v>
+        <v>3.8184</v>
       </c>
       <c r="C19" t="n">
-        <v>2.2433</v>
+        <v>2.3537</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0325</v>
+        <v>1.0918</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6393</v>
+        <v>3.8184</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6393</v>
+        <v>3.6394</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2403</v>
+        <v>5.2406</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2403</v>
+        <v>5.2406</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.2403</v>
+        <v>5.2406</v>
       </c>
       <c r="N19" t="n">
         <v>274</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.525</v>
+        <v>3.5082</v>
       </c>
       <c r="C20" t="n">
-        <v>2.1728</v>
+        <v>2.1625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9804</v>
+        <v>0.9532</v>
       </c>
       <c r="E20" t="n">
-        <v>3.525</v>
+        <v>3.5082</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8624</v>
+        <v>2.8454</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6626</v>
+        <v>0.663</v>
       </c>
       <c r="H20" t="n">
-        <v>3.54</v>
+        <v>3.5027</v>
       </c>
       <c r="I20" t="n">
-        <v>3.54</v>
+        <v>3.5027</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6626</v>
+        <v>0.663</v>
       </c>
       <c r="K20" t="n">
         <v>143</v>
@@ -1357,7 +1357,7 @@
         <v>183</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2026</v>
+        <v>4.1657</v>
       </c>
       <c r="N20" t="n">
         <v>326</v>
@@ -1366,185 +1366,185 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.3937</v>
+        <v>3.4867</v>
       </c>
       <c r="C21" t="n">
-        <v>2.0919</v>
+        <v>2.1492</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9207</v>
+        <v>0.9436</v>
       </c>
       <c r="E21" t="n">
-        <v>3.3937</v>
+        <v>3.4867</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3937</v>
+        <v>1.9987</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7028</v>
+        <v>1.9987</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7028</v>
+        <v>2.0502</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="K21" t="n">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M21" t="n">
-        <v>4.7028</v>
+        <v>3.468</v>
       </c>
       <c r="N21" t="n">
-        <v>285</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.385</v>
+        <v>3.4522</v>
       </c>
       <c r="C22" t="n">
-        <v>2.0865</v>
+        <v>2.1279</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9167</v>
+        <v>0.9282</v>
       </c>
       <c r="E22" t="n">
-        <v>3.385</v>
+        <v>3.4522</v>
       </c>
       <c r="F22" t="n">
-        <v>1.999</v>
+        <v>3.3938</v>
       </c>
       <c r="G22" t="n">
-        <v>1.386</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.999</v>
+        <v>4.703</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0506</v>
+        <v>4.703</v>
       </c>
       <c r="J22" t="n">
-        <v>1.386</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>219</v>
+        <v>285</v>
       </c>
       <c r="L22" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4366</v>
+        <v>4.703</v>
       </c>
       <c r="N22" t="n">
-        <v>336</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.2487</v>
+        <v>3.3591</v>
       </c>
       <c r="C23" t="n">
-        <v>2.0025</v>
+        <v>2.0706</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8547</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2487</v>
+        <v>3.3591</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0418</v>
+        <v>2.7455</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2069</v>
+        <v>0.4624</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0418</v>
+        <v>3.2842</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0944</v>
+        <v>3.3688</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2069</v>
+        <v>0.4624</v>
       </c>
       <c r="K23" t="n">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="L23" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3013</v>
+        <v>3.8312</v>
       </c>
       <c r="N23" t="n">
-        <v>336</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.208</v>
+        <v>3.1646</v>
       </c>
       <c r="C24" t="n">
-        <v>1.9774</v>
+        <v>1.9507</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8361</v>
+        <v>0.7997</v>
       </c>
       <c r="E24" t="n">
-        <v>3.208</v>
+        <v>3.1646</v>
       </c>
       <c r="F24" t="n">
-        <v>2.7458</v>
+        <v>2.0414</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4622</v>
+        <v>1.2269</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2848</v>
+        <v>2.0414</v>
       </c>
       <c r="I24" t="n">
-        <v>3.3694</v>
+        <v>2.094</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4622</v>
+        <v>1.2269</v>
       </c>
       <c r="K24" t="n">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="L24" t="n">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8316</v>
+        <v>3.3209</v>
       </c>
       <c r="N24" t="n">
-        <v>313</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.144</v>
+        <v>3.1501</v>
       </c>
       <c r="C25" t="n">
-        <v>1.938</v>
+        <v>1.9417</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.7933</v>
       </c>
       <c r="E25" t="n">
-        <v>3.144</v>
+        <v>3.1501</v>
       </c>
       <c r="F25" t="n">
-        <v>3.0861</v>
+        <v>3.0862</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0579</v>
+        <v>0.0576</v>
       </c>
       <c r="H25" t="n">
-        <v>4.0296</v>
+        <v>4.0298</v>
       </c>
       <c r="I25" t="n">
-        <v>4.0296</v>
+        <v>4.0298</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0579</v>
+        <v>0.0576</v>
       </c>
       <c r="K25" t="n">
         <v>181</v>
@@ -1587,7 +1587,7 @@
         <v>62</v>
       </c>
       <c r="M25" t="n">
-        <v>4.0875</v>
+        <v>4.0874</v>
       </c>
       <c r="N25" t="n">
         <v>243</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.9953</v>
+        <v>3.1258</v>
       </c>
       <c r="C26" t="n">
-        <v>1.8463</v>
+        <v>1.9268</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7393</v>
+        <v>0.7824</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9953</v>
+        <v>3.1258</v>
       </c>
       <c r="F26" t="n">
-        <v>3.3295</v>
+        <v>3.3299</v>
       </c>
       <c r="G26" t="n">
         <v>-0.3342</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5624</v>
+        <v>4.5632</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5624</v>
+        <v>4.5632</v>
       </c>
       <c r="J26" t="n">
         <v>-0.3342</v>
@@ -1633,7 +1633,7 @@
         <v>71</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2282</v>
+        <v>4.229</v>
       </c>
       <c r="N26" t="n">
         <v>308</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.8792</v>
+        <v>2.8897</v>
       </c>
       <c r="C27" t="n">
-        <v>1.7747</v>
+        <v>1.7812</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6865</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>2.8792</v>
+        <v>2.8897</v>
       </c>
       <c r="F27" t="n">
-        <v>3.4074</v>
+        <v>3.4073</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5282</v>
+        <v>-0.5201</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7327</v>
+        <v>4.7325</v>
       </c>
       <c r="I27" t="n">
-        <v>4.8546</v>
+        <v>4.8544</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5282</v>
+        <v>-0.5201</v>
       </c>
       <c r="K27" t="n">
         <v>219</v>
@@ -1679,7 +1679,7 @@
         <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3264</v>
+        <v>4.3343</v>
       </c>
       <c r="N27" t="n">
         <v>336</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.6285</v>
+        <v>2.6204</v>
       </c>
       <c r="C28" t="n">
-        <v>1.6202</v>
+        <v>1.6152</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5723</v>
+        <v>0.5567</v>
       </c>
       <c r="E28" t="n">
-        <v>2.6285</v>
+        <v>2.6204</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8415</v>
+        <v>2.8416</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.213</v>
+        <v>-0.1995</v>
       </c>
       <c r="H28" t="n">
-        <v>3.4942</v>
+        <v>3.4945</v>
       </c>
       <c r="I28" t="n">
-        <v>3.4942</v>
+        <v>3.4945</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.213</v>
+        <v>-0.1995</v>
       </c>
       <c r="K28" t="n">
         <v>181</v>
@@ -1725,7 +1725,7 @@
         <v>62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2812</v>
+        <v>3.295</v>
       </c>
       <c r="N28" t="n">
         <v>243</v>
@@ -1734,35 +1734,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.4583</v>
+        <v>2.5423</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5153</v>
+        <v>1.5671</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4949</v>
+        <v>0.5218</v>
       </c>
       <c r="E29" t="n">
-        <v>2.4583</v>
+        <v>2.5423</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8496</v>
+        <v>2.5789</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3913</v>
+        <v>-0.1944</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5119</v>
+        <v>2.9195</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5119</v>
+        <v>2.9195</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3913</v>
+        <v>-0.1944</v>
       </c>
       <c r="K29" t="n">
         <v>140</v>
@@ -1771,7 +1771,7 @@
         <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1206</v>
+        <v>2.7251</v>
       </c>
       <c r="N29" t="n">
         <v>180</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.3846</v>
+        <v>2.4575</v>
       </c>
       <c r="C30" t="n">
-        <v>1.4699</v>
+        <v>1.5148</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4613</v>
+        <v>0.4839</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3846</v>
+        <v>2.4575</v>
       </c>
       <c r="F30" t="n">
-        <v>2.5788</v>
+        <v>2.3119</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1942</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.9192</v>
+        <v>2.3352</v>
       </c>
       <c r="I30" t="n">
-        <v>2.9192</v>
+        <v>2.3352</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1942</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.725</v>
+        <v>2.3352</v>
       </c>
       <c r="N30" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.3438</v>
+        <v>2.3686</v>
       </c>
       <c r="C31" t="n">
-        <v>1.4447</v>
+        <v>1.46</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4427</v>
+        <v>0.4442</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3438</v>
+        <v>2.3686</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3438</v>
+        <v>2.8498</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.3713</v>
       </c>
       <c r="H31" t="n">
-        <v>2.4049</v>
+        <v>3.5123</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4049</v>
+        <v>3.5123</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.3713</v>
       </c>
       <c r="K31" t="n">
-        <v>274</v>
+        <v>140</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M31" t="n">
-        <v>2.4049</v>
+        <v>3.141</v>
       </c>
       <c r="N31" t="n">
-        <v>274</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.3123</v>
+        <v>2.2958</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4253</v>
+        <v>1.4151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4284</v>
+        <v>0.4117</v>
       </c>
       <c r="E32" t="n">
-        <v>2.3123</v>
+        <v>2.2958</v>
       </c>
       <c r="F32" t="n">
-        <v>2.3123</v>
+        <v>2.3439</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3359</v>
+        <v>2.4052</v>
       </c>
       <c r="I32" t="n">
-        <v>2.3359</v>
+        <v>2.4052</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.3359</v>
+        <v>2.4052</v>
       </c>
       <c r="N32" t="n">
-        <v>186</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.1596</v>
+        <v>2.194</v>
       </c>
       <c r="C33" t="n">
-        <v>1.3312</v>
+        <v>1.3524</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3589</v>
+        <v>0.3662</v>
       </c>
       <c r="E33" t="n">
-        <v>2.1596</v>
+        <v>2.194</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1596</v>
+        <v>2.1601</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1596</v>
+        <v>2.1601</v>
       </c>
       <c r="I33" t="n">
-        <v>2.1596</v>
+        <v>2.1601</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.1596</v>
+        <v>2.1601</v>
       </c>
       <c r="N33" t="n">
         <v>185</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.5833</v>
+        <v>1.6187</v>
       </c>
       <c r="C34" t="n">
-        <v>0.976</v>
+        <v>0.9978</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0965</v>
+        <v>0.1092</v>
       </c>
       <c r="E34" t="n">
-        <v>1.5833</v>
+        <v>1.6187</v>
       </c>
       <c r="F34" t="n">
-        <v>2.3442</v>
+        <v>1.5176</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7609</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4058</v>
+        <v>1.5176</v>
       </c>
       <c r="I34" t="n">
-        <v>2.4058</v>
+        <v>1.5176</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7609</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="L34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.6449</v>
+        <v>1.5176</v>
       </c>
       <c r="N34" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.5176</v>
+        <v>1.5774</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9355</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>1.5176</v>
+        <v>1.5774</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5176</v>
+        <v>2.3371</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.7611</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5176</v>
+        <v>2.3903</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5176</v>
+        <v>2.3903</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.7611</v>
       </c>
       <c r="K35" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5176</v>
+        <v>1.6292</v>
       </c>
       <c r="N35" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4598</v>
+        <v>1.5402</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8998</v>
+        <v>0.9494</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0403</v>
+        <v>0.0742</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4598</v>
+        <v>1.5402</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5685</v>
       </c>
       <c r="G36" t="n">
         <v>0.8686</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5685</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5685</v>
       </c>
       <c r="J36" t="n">
         <v>0.8686</v>
@@ -2093,7 +2093,7 @@
         <v>71</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4598</v>
+        <v>1.4371</v>
       </c>
       <c r="N36" t="n">
         <v>308</v>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4382</v>
+        <v>1.5104</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8865</v>
+        <v>0.931</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0305</v>
+        <v>0.0608</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4382</v>
+        <v>1.5104</v>
       </c>
       <c r="F37" t="n">
         <v>1.6417</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cairne</t>
+          <t>Dawy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3924</v>
+        <v>1.4636</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8583</v>
+        <v>0.9022</v>
       </c>
       <c r="D38" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0399</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3924</v>
+        <v>1.4636</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3924</v>
+        <v>1.2065</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3924</v>
+        <v>1.2065</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3924</v>
+        <v>1.2065</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3924</v>
+        <v>1.2065</v>
       </c>
       <c r="N38" t="n">
         <v>176</v>
@@ -2194,78 +2194,78 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sausol</t>
+          <t>cairne</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3492</v>
+        <v>1.4254</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8317</v>
+        <v>0.8786</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.01</v>
+        <v>0.0229</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3492</v>
+        <v>1.4254</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3492</v>
+        <v>1.3923</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.3492</v>
+        <v>1.3923</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3492</v>
+        <v>1.3923</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3492</v>
+        <v>1.3923</v>
       </c>
       <c r="N39" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dawy</t>
+          <t>Flierax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.2071</v>
+        <v>1.335</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7441</v>
+        <v>0.8229</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0747</v>
+        <v>-0.0175</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2071</v>
+        <v>1.335</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2071</v>
+        <v>1.1228</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2071</v>
+        <v>1.1228</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2071</v>
+        <v>1.1228</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.2071</v>
+        <v>1.1228</v>
       </c>
       <c r="N40" t="n">
         <v>176</v>
@@ -2286,93 +2286,93 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>sausol</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.1725</v>
+        <v>1.3302</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7227</v>
+        <v>0.8199</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0905</v>
+        <v>-0.0196</v>
       </c>
       <c r="E41" t="n">
-        <v>1.1725</v>
+        <v>1.3302</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1725</v>
+        <v>1.349</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1725</v>
+        <v>1.349</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1725</v>
+        <v>1.349</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1725</v>
+        <v>1.349</v>
       </c>
       <c r="N41" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Flierax</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.1141</v>
+        <v>1.2534</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6867</v>
+        <v>0.7726</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.117</v>
+        <v>-0.054</v>
       </c>
       <c r="E42" t="n">
-        <v>1.1141</v>
+        <v>1.2534</v>
       </c>
       <c r="F42" t="n">
-        <v>1.1141</v>
+        <v>1.1725</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.1141</v>
+        <v>1.1725</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1141</v>
+        <v>1.1725</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1141</v>
+        <v>1.1725</v>
       </c>
       <c r="N42" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43">
@@ -2382,31 +2382,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.0727</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6612</v>
+        <v>0.5738</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1359</v>
+        <v>-0.198</v>
       </c>
       <c r="E43" t="n">
-        <v>1.0727</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>1.5608</v>
+        <v>1.5612</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.4881</v>
+        <v>-0.4886</v>
       </c>
       <c r="H43" t="n">
-        <v>1.5608</v>
+        <v>1.5612</v>
       </c>
       <c r="I43" t="n">
-        <v>1.5608</v>
+        <v>1.5612</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4881</v>
+        <v>-0.4886</v>
       </c>
       <c r="K43" t="n">
         <v>181</v>
@@ -2415,7 +2415,7 @@
         <v>62</v>
       </c>
       <c r="M43" t="n">
-        <v>1.0727</v>
+        <v>1.0726</v>
       </c>
       <c r="N43" t="n">
         <v>243</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.025</v>
+        <v>0.928</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6318</v>
+        <v>0.572</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1576</v>
+        <v>-0.1993</v>
       </c>
       <c r="E44" t="n">
-        <v>1.025</v>
+        <v>0.928</v>
       </c>
       <c r="F44" t="n">
-        <v>1.025</v>
+        <v>1.0551</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.025</v>
+        <v>1.0551</v>
       </c>
       <c r="I44" t="n">
-        <v>1.025</v>
+        <v>1.0551</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.025</v>
+        <v>1.0551</v>
       </c>
       <c r="N44" t="n">
         <v>186</v>
@@ -2470,415 +2470,415 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9391</v>
+        <v>0.913</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5789</v>
+        <v>0.5628</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1967</v>
+        <v>-0.206</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9391</v>
+        <v>0.913</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9391</v>
+        <v>0.9225</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9391</v>
+        <v>0.9225</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9391</v>
+        <v>0.9225</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9391</v>
+        <v>0.9225</v>
       </c>
       <c r="N45" t="n">
-        <v>142</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9223</v>
+        <v>0.8989</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5685</v>
+        <v>0.5541</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2044</v>
+        <v>-0.2123</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9223</v>
+        <v>0.8989</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9223</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9223</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.9223</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>285</v>
+        <v>175</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9223</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>285</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9144</v>
+        <v>0.8541</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5636</v>
+        <v>0.5265</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2079</v>
+        <v>-0.2323</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9144</v>
+        <v>0.8541</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9144</v>
+        <v>0.9391</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9144</v>
+        <v>0.9391</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9144</v>
+        <v>0.9391</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.9144</v>
+        <v>0.9391</v>
       </c>
       <c r="N47" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.7831</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5204</v>
+        <v>0.4827</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2399</v>
+        <v>-0.264</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.7831</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5</v>
+        <v>0.675</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5</v>
+        <v>0.675</v>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.675</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="L48" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="N48" t="n">
-        <v>326</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.6954</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5036</v>
+        <v>0.4286</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2523</v>
+        <v>-0.3032</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.6954</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.5422</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.6553</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.5422</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8169999999999999</v>
+        <v>1.5422</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.6553</v>
       </c>
       <c r="K49" t="n">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8869</v>
       </c>
       <c r="N49" t="n">
-        <v>175</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6254</v>
       </c>
       <c r="C50" t="n">
-        <v>0.439</v>
+        <v>0.3855</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3</v>
+        <v>-0.3345</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.6254</v>
       </c>
       <c r="F50" t="n">
-        <v>1.6802</v>
+        <v>0.9144</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.968</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.6802</v>
+        <v>0.9144</v>
       </c>
       <c r="I50" t="n">
-        <v>1.7235</v>
+        <v>0.9144</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.968</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="L50" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.9144</v>
       </c>
       <c r="N50" t="n">
-        <v>313</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.675</v>
+        <v>0.6244</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4161</v>
+        <v>0.3849</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3169</v>
+        <v>-0.3349</v>
       </c>
       <c r="E51" t="n">
-        <v>0.675</v>
+        <v>0.6244</v>
       </c>
       <c r="F51" t="n">
-        <v>0.675</v>
+        <v>1.6799</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.9775</v>
       </c>
       <c r="H51" t="n">
-        <v>0.675</v>
+        <v>1.6799</v>
       </c>
       <c r="I51" t="n">
-        <v>0.675</v>
+        <v>1.7232</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.9775</v>
       </c>
       <c r="K51" t="n">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M51" t="n">
-        <v>0.675</v>
+        <v>0.7457</v>
       </c>
       <c r="N51" t="n">
-        <v>274</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5673</v>
+        <v>0.5919</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3497</v>
+        <v>0.3648</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.366</v>
+        <v>-0.3494</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5673</v>
+        <v>0.5919</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5673</v>
+        <v>0.4299</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5673</v>
+        <v>0.4299</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5673</v>
+        <v>0.4299</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5673</v>
+        <v>0.4299</v>
       </c>
       <c r="N52" t="n">
-        <v>142</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4453</v>
+        <v>0.4899</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2745</v>
+        <v>0.302</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4215</v>
+        <v>-0.395</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4453</v>
+        <v>0.4899</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4453</v>
+        <v>0.5673</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4453</v>
+        <v>0.5673</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4453</v>
+        <v>0.5673</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>285</v>
+        <v>142</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4453</v>
+        <v>0.5673</v>
       </c>
       <c r="N53" t="n">
-        <v>285</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0929</v>
+        <v>0.3677</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0573</v>
+        <v>0.2267</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5819</v>
+        <v>-0.4496</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0929</v>
+        <v>0.3677</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0929</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0929</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0929</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0929</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="N54" t="n">
         <v>135</v>
@@ -2930,139 +2930,139 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0692</v>
+        <v>0.0127</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0427</v>
+        <v>0.0078</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5927</v>
+        <v>-0.6081</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0692</v>
+        <v>0.0127</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0692</v>
+        <v>0.0455</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0692</v>
+        <v>0.0455</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0692</v>
+        <v>0.0455</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0692</v>
+        <v>0.0455</v>
       </c>
       <c r="N55" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0038</v>
+        <v>-0.1091</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0023</v>
+        <v>-0.0672</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6626</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0038</v>
+        <v>-0.1091</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0038</v>
+        <v>-0.0706</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0038</v>
+        <v>-0.0706</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0038</v>
+        <v>-0.0706</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0038</v>
+        <v>-0.0706</v>
       </c>
       <c r="N56" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0706</v>
+        <v>-0.1656</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0435</v>
+        <v>-0.1021</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6563</v>
+        <v>-0.6878</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0706</v>
+        <v>-0.1656</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0706</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.0706</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0706</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0706</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>142</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58">
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.0954</v>
+        <v>-0.1872</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0588</v>
+        <v>-0.1154</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6676</v>
+        <v>-0.6974</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.0954</v>
+        <v>-0.1872</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.0954</v>
+        <v>-0.0956</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.0954</v>
+        <v>-0.0956</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0954</v>
+        <v>-0.0956</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.0954</v>
+        <v>-0.0956</v>
       </c>
       <c r="N58" t="n">
         <v>186</v>
@@ -3114,507 +3114,507 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4333</v>
+        <v>-0.3099</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2671</v>
+        <v>-0.191</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.8215</v>
+        <v>-0.7522</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4333</v>
+        <v>-0.3099</v>
       </c>
       <c r="F59" t="n">
-        <v>1.2326</v>
+        <v>-0.4552</v>
       </c>
       <c r="G59" t="n">
-        <v>-1.6659</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.2326</v>
+        <v>-0.4552</v>
       </c>
       <c r="I59" t="n">
-        <v>1.2326</v>
+        <v>-0.4552</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.6659</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>227</v>
+        <v>142</v>
       </c>
       <c r="L59" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4333</v>
+        <v>-0.4552</v>
       </c>
       <c r="N59" t="n">
-        <v>352</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4457</v>
+        <v>-0.6421</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2747</v>
+        <v>-0.3958</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.9006</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4457</v>
+        <v>-0.6421</v>
       </c>
       <c r="F60" t="n">
-        <v>1.2503</v>
+        <v>-0.517</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.696</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.2503</v>
+        <v>-0.517</v>
       </c>
       <c r="I60" t="n">
-        <v>1.2503</v>
+        <v>-0.517</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.696</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="L60" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.4457</v>
+        <v>-0.517</v>
       </c>
       <c r="N60" t="n">
-        <v>366</v>
+        <v>185</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4552</v>
+        <v>-0.6556</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2806</v>
+        <v>-0.4041</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8314</v>
+        <v>-0.9067</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4552</v>
+        <v>-0.6556</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4552</v>
+        <v>-0.7585</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4552</v>
+        <v>-0.7585</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4552</v>
+        <v>-0.7585</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.4552</v>
+        <v>-0.7585</v>
       </c>
       <c r="N61" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>kade0</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.6969</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3184</v>
+        <v>-0.4296</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.9251</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.6969</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5996</v>
       </c>
       <c r="N62" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kade0</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5994</v>
+        <v>-0.6982</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3695</v>
+        <v>-0.4304</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8971</v>
+        <v>-0.9257</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5994</v>
+        <v>-0.6982</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5994</v>
+        <v>-1.2313</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.5923</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5994</v>
+        <v>-1.2313</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5994</v>
+        <v>-1.2313</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.5923</v>
       </c>
       <c r="K63" t="n">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.5994</v>
+        <v>-0.639</v>
       </c>
       <c r="N63" t="n">
-        <v>186</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.7013</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3775</v>
+        <v>-0.4323</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.903</v>
+        <v>-0.9271</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.7013</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6124000000000001</v>
+        <v>1.2434</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-1.6661</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6124000000000001</v>
+        <v>1.2434</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6124000000000001</v>
+        <v>1.2434</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-1.6661</v>
       </c>
       <c r="K64" t="n">
-        <v>285</v>
+        <v>227</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.4226999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>285</v>
+        <v>352</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4166</v>
+        <v>-0.4384</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9319</v>
+        <v>-0.9315</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.2682</v>
+        <v>1.2496</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5923</v>
+        <v>-1.6957</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.2682</v>
+        <v>1.2496</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.2682</v>
+        <v>1.2496</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5923</v>
+        <v>-1.6957</v>
       </c>
       <c r="K65" t="n">
-        <v>237</v>
+        <v>156</v>
       </c>
       <c r="L65" t="n">
-        <v>71</v>
+        <v>210</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.4460999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>308</v>
+        <v>366</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dukefissura</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7056</v>
+        <v>-0.7366</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4349</v>
+        <v>-0.454</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9454</v>
+        <v>-0.9428</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7056</v>
+        <v>-0.7366</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7056</v>
+        <v>-0.6122</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7056</v>
+        <v>-0.6122</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7056</v>
+        <v>-0.6122</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>186</v>
+        <v>285</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7056</v>
+        <v>-0.6122</v>
       </c>
       <c r="N66" t="n">
-        <v>186</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>dukefissura</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.758</v>
+        <v>-0.7739</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4672</v>
+        <v>-0.477</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-0.9595</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.758</v>
+        <v>-0.7739</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.758</v>
+        <v>-0.7059</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.758</v>
+        <v>-0.7059</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.758</v>
+        <v>-0.7059</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.758</v>
+        <v>-0.7059</v>
       </c>
       <c r="N67" t="n">
-        <v>135</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.7846</v>
+        <v>-0.8329</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4836</v>
+        <v>-0.5134</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.9859</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.7846</v>
+        <v>-0.8329</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.7846</v>
+        <v>-0.7956</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.7846</v>
+        <v>-0.7956</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7846</v>
+        <v>-0.7956</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>285</v>
+        <v>142</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.7846</v>
+        <v>-0.7956</v>
       </c>
       <c r="N68" t="n">
-        <v>285</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.7956</v>
+        <v>-0.8811</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4904</v>
+        <v>-0.5431</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-1.0074</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.7956</v>
+        <v>-0.8811</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.7956</v>
+        <v>-0.7845</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.7956</v>
+        <v>-0.7845</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.7956</v>
+        <v>-0.7845</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>142</v>
+        <v>285</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.7956</v>
+        <v>-0.7845</v>
       </c>
       <c r="N69" t="n">
-        <v>142</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70">
@@ -3624,16 +3624,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9462</v>
+        <v>-1.0732</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.6615</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0549</v>
+        <v>-1.0932</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9462</v>
+        <v>-1.0732</v>
       </c>
       <c r="F70" t="n">
         <v>-0.9462</v>
@@ -3666,93 +3666,93 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nifee</t>
+          <t>dav1g</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.994</v>
+        <v>-1.183</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6127</v>
+        <v>-0.7292</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0767</v>
+        <v>-1.1422</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.994</v>
+        <v>-1.183</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.994</v>
+        <v>-1.1498</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.994</v>
+        <v>-1.1498</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.994</v>
+        <v>-1.1498</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.994</v>
+        <v>-1.1498</v>
       </c>
       <c r="N71" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dav1g</t>
+          <t>nifee</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1498</v>
+        <v>-1.2814</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7087</v>
+        <v>-0.7899</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1476</v>
+        <v>-1.1862</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1498</v>
+        <v>-1.2814</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.1498</v>
+        <v>-0.9942</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.1498</v>
+        <v>-0.9942</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.1498</v>
+        <v>-0.9942</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.1498</v>
+        <v>-0.9942</v>
       </c>
       <c r="N72" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="73">
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.25</v>
+        <v>-1.5085</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7705</v>
+        <v>-0.9298</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1932</v>
+        <v>-1.2876</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.25</v>
+        <v>-1.5085</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.006</v>
+        <v>-1.0058</v>
       </c>
       <c r="G73" t="n">
         <v>-0.244</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.006</v>
+        <v>-1.0058</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.006</v>
+        <v>-1.0058</v>
       </c>
       <c r="J73" t="n">
         <v>-0.244</v>
@@ -3795,7 +3795,7 @@
         <v>71</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.25</v>
+        <v>-1.2498</v>
       </c>
       <c r="N73" t="n">
         <v>308</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.4266</v>
+        <v>-1.6368</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8794</v>
+        <v>-1.0089</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2736</v>
+        <v>-1.3449</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.4266</v>
+        <v>-1.6368</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.4266</v>
+        <v>-1.4273</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.4266</v>
+        <v>-1.4273</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.4266</v>
+        <v>-1.4273</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.4266</v>
+        <v>-1.4273</v>
       </c>
       <c r="N74" t="n">
         <v>135</v>
@@ -3850,93 +3850,93 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.6491</v>
+        <v>-1.8646</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.0165</v>
+        <v>-1.1493</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3749</v>
+        <v>-1.4467</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.6491</v>
+        <v>-1.8646</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.7211</v>
+        <v>-1.6501</v>
       </c>
       <c r="G75" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.7211</v>
+        <v>-1.6501</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.7654</v>
+        <v>-1.6501</v>
       </c>
       <c r="J75" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="L75" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.6934</v>
+        <v>-1.6501</v>
       </c>
       <c r="N75" t="n">
-        <v>313</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.6494</v>
+        <v>-1.935</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.0167</v>
+        <v>-1.1927</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.375</v>
+        <v>-1.4781</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.6494</v>
+        <v>-1.935</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.6494</v>
+        <v>-1.7213</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>0.0722</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.6494</v>
+        <v>-1.7213</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.6494</v>
+        <v>-1.7657</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>0.0722</v>
       </c>
       <c r="K76" t="n">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.6494</v>
+        <v>-1.6935</v>
       </c>
       <c r="N76" t="n">
-        <v>135</v>
+        <v>313</v>
       </c>
     </row>
     <row r="77">
@@ -3946,31 +3946,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.0406</v>
+        <v>-2.4208</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.2578</v>
+        <v>-1.4922</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5531</v>
+        <v>-1.6951</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.0406</v>
+        <v>-2.4208</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.5251</v>
+        <v>-1.4956</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.5155</v>
+        <v>-0.5157</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.5251</v>
+        <v>-1.4956</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.5251</v>
+        <v>-1.4956</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.5155</v>
+        <v>-0.5157</v>
       </c>
       <c r="K77" t="n">
         <v>140</v>
@@ -3979,7 +3979,7 @@
         <v>40</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.0406</v>
+        <v>-2.0113</v>
       </c>
       <c r="N77" t="n">
         <v>180</v>
@@ -3992,31 +3992,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.3601</v>
+        <v>-2.6412</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.4548</v>
+        <v>-1.628</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.6986</v>
+        <v>-1.7936</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.3601</v>
+        <v>-2.6412</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.5273</v>
+        <v>-0.5182</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.8328</v>
+        <v>-1.8579</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.5273</v>
+        <v>-0.5182</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5273</v>
+        <v>-0.5182</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.8328</v>
+        <v>-1.8579</v>
       </c>
       <c r="K78" t="n">
         <v>143</v>
@@ -4025,7 +4025,7 @@
         <v>183</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.3601</v>
+        <v>-2.3761</v>
       </c>
       <c r="N78" t="n">
         <v>326</v>
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.6667</v>
+        <v>-2.9699</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.6438</v>
+        <v>-1.8307</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.8381</v>
+        <v>-1.9404</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.6667</v>
+        <v>-2.9699</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.8293</v>
+        <v>-1.829</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.8374</v>
+        <v>-0.8378</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.8293</v>
+        <v>-1.829</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.8293</v>
+        <v>-1.829</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.8374</v>
+        <v>-0.8378</v>
       </c>
       <c r="K79" t="n">
         <v>227</v>
@@ -4071,7 +4071,7 @@
         <v>125</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.6667</v>
+        <v>-2.6668</v>
       </c>
       <c r="N79" t="n">
         <v>352</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.7194</v>
+        <v>-3.2274</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6762</v>
+        <v>-1.9894</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8621</v>
+        <v>-2.0554</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.7194</v>
+        <v>-3.2274</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.7194</v>
+        <v>-2.7197</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.7194</v>
+        <v>-2.7197</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.7194</v>
+        <v>-2.7197</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.7194</v>
+        <v>-2.7197</v>
       </c>
       <c r="N80" t="n">
         <v>176</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.5213</v>
+        <v>-4.009</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.1705</v>
+        <v>-2.4712</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2272</v>
+        <v>-2.4046</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.5213</v>
+        <v>-4.009</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.5213</v>
+        <v>-3.5436</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.5213</v>
+        <v>-3.5436</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.5213</v>
+        <v>-3.5436</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.5213</v>
+        <v>-3.5436</v>
       </c>
       <c r="N81" t="n">
         <v>274</v>
@@ -5669,10 +5669,10 @@
         <v>1.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9375</v>
+        <v>0.9384</v>
       </c>
       <c r="J37" t="n">
-        <v>18.75</v>
+        <v>18.768</v>
       </c>
     </row>
     <row r="38">
@@ -5706,13 +5706,13 @@
         <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3511</v>
+        <v>0.3327</v>
       </c>
       <c r="J38" t="n">
-        <v>7.022</v>
+        <v>6.654</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.348</v>
+        <v>-0.3478</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.96</v>
+        <v>-6.956</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.65</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3844</v>
+        <v>-0.3842</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.688</v>
+        <v>-7.684</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.55</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4726</v>
+        <v>-0.4724</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.452</v>
+        <v>-9.448</v>
       </c>
     </row>
     <row r="42">
@@ -7069,10 +7069,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5174</v>
+        <v>0.517</v>
       </c>
       <c r="J72" t="n">
-        <v>10.8654</v>
+        <v>10.857</v>
       </c>
     </row>
     <row r="73">
@@ -7106,13 +7106,13 @@
         <v>21</v>
       </c>
       <c r="H73" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3739</v>
+        <v>0.3912</v>
       </c>
       <c r="J73" t="n">
-        <v>7.8519</v>
+        <v>8.215199999999999</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0229</v>
+        <v>-0.023</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.4809</v>
+        <v>-0.483</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.71</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3346</v>
+        <v>-0.3348</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.0266</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.67</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3713</v>
+        <v>-0.3715</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.7973</v>
+        <v>-7.8015</v>
       </c>
     </row>
     <row r="77">
@@ -7469,10 +7469,10 @@
         <v>1.4</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6703</v>
+        <v>0.6698</v>
       </c>
       <c r="J82" t="n">
-        <v>19.4387</v>
+        <v>19.4242</v>
       </c>
     </row>
     <row r="83">
@@ -7506,13 +7506,13 @@
         <v>29</v>
       </c>
       <c r="H83" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2913</v>
+        <v>0.3096</v>
       </c>
       <c r="J83" t="n">
-        <v>8.447699999999999</v>
+        <v>8.978400000000001</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.8</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2522</v>
+        <v>-0.2524</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.3138</v>
+        <v>-7.3196</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.67</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3749</v>
+        <v>-0.375</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.8721</v>
+        <v>-10.875</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.42</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.871</v>
       </c>
       <c r="J87" t="n">
-        <v>25.2445</v>
+        <v>25.259</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I88" t="n">
-        <v>0.444</v>
+        <v>0.4443</v>
       </c>
       <c r="J88" t="n">
-        <v>12.876</v>
+        <v>12.8847</v>
       </c>
     </row>
     <row r="89">
@@ -7746,13 +7746,13 @@
         <v>29</v>
       </c>
       <c r="H89" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3507</v>
+        <v>0.3256</v>
       </c>
       <c r="J89" t="n">
-        <v>10.1703</v>
+        <v>9.442399999999999</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3048</v>
+        <v>-0.3044</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.8392</v>
+        <v>-8.8276</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.511</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.819</v>
+        <v>-14.8074</v>
       </c>
     </row>
     <row r="92">
@@ -8666,13 +8666,13 @@
         <v>20</v>
       </c>
       <c r="H112" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0577</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.428</v>
+        <v>-1.154</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0848</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.696</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.92</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.11</v>
+        <v>-0.1102</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.2</v>
+        <v>-2.204</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.72</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3128</v>
+        <v>-0.313</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.256</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.64</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3859</v>
+        <v>-0.3861</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.718</v>
+        <v>-7.722</v>
       </c>
     </row>
     <row r="117">
@@ -9066,13 +9066,13 @@
         <v>20</v>
       </c>
       <c r="H122" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I122" t="n">
-        <v>0.664</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>13.28</v>
+        <v>13.498</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.01</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0523</v>
+        <v>0.052</v>
       </c>
       <c r="J123" t="n">
-        <v>1.046</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0687</v>
+        <v>-0.0689</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.374</v>
+        <v>-1.378</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1303</v>
+        <v>-0.1304</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.606</v>
+        <v>-2.608</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.42</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.5853</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.704</v>
+        <v>-11.706</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.68</v>
       </c>
       <c r="I127" t="n">
-        <v>1.188</v>
+        <v>1.1885</v>
       </c>
       <c r="J127" t="n">
-        <v>23.76</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="128">
@@ -9306,13 +9306,13 @@
         <v>20</v>
       </c>
       <c r="H128" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7101</v>
+        <v>0.6958</v>
       </c>
       <c r="J128" t="n">
-        <v>14.202</v>
+        <v>13.916</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.17</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4648</v>
+        <v>0.4651</v>
       </c>
       <c r="J129" t="n">
-        <v>9.295999999999999</v>
+        <v>9.302</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0611</v>
+        <v>0.0614</v>
       </c>
       <c r="J130" t="n">
-        <v>1.222</v>
+        <v>1.228</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.99</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1</v>
+        <v>-0.0997</v>
       </c>
       <c r="J131" t="n">
-        <v>-2</v>
+        <v>-1.994</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.31</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5707</v>
       </c>
       <c r="J132" t="n">
-        <v>12.5642</v>
+        <v>12.5554</v>
       </c>
     </row>
     <row r="133">
@@ -9506,13 +9506,13 @@
         <v>22</v>
       </c>
       <c r="H133" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2152</v>
+        <v>0.2352</v>
       </c>
       <c r="J133" t="n">
-        <v>4.7344</v>
+        <v>5.1744</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.93</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1102</v>
+        <v>-0.1104</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.4244</v>
+        <v>-2.4288</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1223</v>
+        <v>-0.1225</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.6906</v>
+        <v>-2.695</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.68</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3645</v>
+        <v>-0.3647</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.019</v>
+        <v>-8.023400000000001</v>
       </c>
     </row>
     <row r="137">
@@ -10069,10 +10069,10 @@
         <v>2.26</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8225</v>
+        <v>1.8219</v>
       </c>
       <c r="J147" t="n">
-        <v>32.805</v>
+        <v>32.7942</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.81</v>
       </c>
       <c r="I148" t="n">
-        <v>1.3009</v>
+        <v>1.3006</v>
       </c>
       <c r="J148" t="n">
-        <v>23.4162</v>
+        <v>23.4108</v>
       </c>
     </row>
     <row r="149">
@@ -10146,13 +10146,13 @@
         <v>18</v>
       </c>
       <c r="H149" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7024</v>
+        <v>0.7165</v>
       </c>
       <c r="J149" t="n">
-        <v>12.6432</v>
+        <v>12.897</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>1.21</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5049</v>
+        <v>0.5046</v>
       </c>
       <c r="J150" t="n">
-        <v>9.088200000000001</v>
+        <v>9.082800000000001</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.77</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7318</v>
+        <v>-0.732</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.1724</v>
+        <v>-13.176</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.59</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7145</v>
+        <v>0.714</v>
       </c>
       <c r="J152" t="n">
-        <v>21.435</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.41</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5624</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>16.872</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="154">
@@ -10346,13 +10346,13 @@
         <v>30</v>
       </c>
       <c r="H154" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3457</v>
+        <v>-0.3366</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.371</v>
+        <v>-10.098</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3549</v>
+        <v>-0.3551</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.647</v>
+        <v>-10.653</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5213</v>
+        <v>-0.5215</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.639</v>
+        <v>-15.645</v>
       </c>
     </row>
     <row r="157">
@@ -10669,10 +10669,10 @@
         <v>1.69</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2231</v>
+        <v>1.2225</v>
       </c>
       <c r="J162" t="n">
-        <v>25.6851</v>
+        <v>25.6725</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.585</v>
+        <v>0.5847</v>
       </c>
       <c r="J163" t="n">
-        <v>12.285</v>
+        <v>12.2787</v>
       </c>
     </row>
     <row r="164">
@@ -10746,13 +10746,13 @@
         <v>21</v>
       </c>
       <c r="H164" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4149</v>
+        <v>0.4359</v>
       </c>
       <c r="J164" t="n">
-        <v>8.712899999999999</v>
+        <v>9.1539</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.9</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3726</v>
+        <v>-0.373</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.8246</v>
+        <v>-7.833</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.82</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5717</v>
+        <v>-0.572</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.0057</v>
+        <v>-12.012</v>
       </c>
     </row>
     <row r="167">
@@ -11069,10 +11069,10 @@
         <v>1.38</v>
       </c>
       <c r="I172" t="n">
-        <v>0.786</v>
+        <v>0.7853</v>
       </c>
       <c r="J172" t="n">
-        <v>13.362</v>
+        <v>13.3501</v>
       </c>
     </row>
     <row r="173">
@@ -11106,13 +11106,13 @@
         <v>17</v>
       </c>
       <c r="H173" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7281</v>
+        <v>0.7421</v>
       </c>
       <c r="J173" t="n">
-        <v>12.3777</v>
+        <v>12.6157</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>1.26</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6089</v>
+        <v>0.6085</v>
       </c>
       <c r="J174" t="n">
-        <v>10.3513</v>
+        <v>10.3445</v>
       </c>
     </row>
     <row r="175">
@@ -11186,13 +11186,13 @@
         <v>17</v>
       </c>
       <c r="H175" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1671</v>
+        <v>0.1966</v>
       </c>
       <c r="J175" t="n">
-        <v>2.8407</v>
+        <v>3.3422</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>1.04</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1354</v>
+        <v>0.1347</v>
       </c>
       <c r="J176" t="n">
-        <v>2.3018</v>
+        <v>2.2899</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.82</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1172</v>
+        <v>1.118</v>
       </c>
       <c r="J177" t="n">
-        <v>18.9924</v>
+        <v>19.006</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>0.87</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1779</v>
+        <v>-0.1777</v>
       </c>
       <c r="J178" t="n">
-        <v>-3.0243</v>
+        <v>-3.0209</v>
       </c>
     </row>
     <row r="179">
@@ -11346,13 +11346,13 @@
         <v>17</v>
       </c>
       <c r="H179" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2697</v>
+        <v>-0.2792</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.5849</v>
+        <v>-4.7464</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3175</v>
+        <v>-0.3173</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.3975</v>
+        <v>-5.3941</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.67</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3727</v>
+        <v>-0.3725</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.3359</v>
+        <v>-6.3325</v>
       </c>
     </row>
     <row r="182">
@@ -13266,13 +13266,13 @@
         <v>15</v>
       </c>
       <c r="H227" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.2252</v>
+        <v>-0.2151</v>
       </c>
       <c r="J227" t="n">
-        <v>-3.378</v>
+        <v>-3.2265</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>0.7</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3059</v>
+        <v>-0.3063</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.5885</v>
+        <v>-4.5945</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.63</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3702</v>
+        <v>-0.3704</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.553</v>
+        <v>-5.556</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.51</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4734</v>
+        <v>-0.4737</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.101</v>
+        <v>-7.1055</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.45</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5262</v>
+        <v>-0.5265</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.893</v>
+        <v>-7.8975</v>
       </c>
     </row>
     <row r="232">
@@ -14466,13 +14466,13 @@
         <v>19</v>
       </c>
       <c r="H257" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I257" t="n">
-        <v>1.0744</v>
+        <v>1.0608</v>
       </c>
       <c r="J257" t="n">
-        <v>20.4136</v>
+        <v>20.1552</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.45</v>
       </c>
       <c r="I258" t="n">
-        <v>1.0162</v>
+        <v>1.0166</v>
       </c>
       <c r="J258" t="n">
-        <v>19.3078</v>
+        <v>19.3154</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.36</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8563</v>
+        <v>0.8566</v>
       </c>
       <c r="J259" t="n">
-        <v>16.2697</v>
+        <v>16.2754</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.07</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2146</v>
+        <v>0.215</v>
       </c>
       <c r="J260" t="n">
-        <v>4.0774</v>
+        <v>4.085</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>1.05</v>
       </c>
       <c r="I261" t="n">
-        <v>0.1553</v>
+        <v>0.1557</v>
       </c>
       <c r="J261" t="n">
-        <v>2.9507</v>
+        <v>2.9583</v>
       </c>
     </row>
     <row r="262">
@@ -16266,13 +16266,13 @@
         <v>20</v>
       </c>
       <c r="H302" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I302" t="n">
-        <v>1.7184</v>
+        <v>1.707</v>
       </c>
       <c r="J302" t="n">
-        <v>34.368</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>1.61</v>
       </c>
       <c r="I303" t="n">
-        <v>1.2315</v>
+        <v>1.2319</v>
       </c>
       <c r="J303" t="n">
-        <v>24.63</v>
+        <v>24.638</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>1.31</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7584</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>15.168</v>
+        <v>15.172</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.79</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.6633</v>
+        <v>-0.663</v>
       </c>
       <c r="J305" t="n">
-        <v>-13.266</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.77</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7081</v>
+        <v>-0.7078</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.162</v>
+        <v>-14.156</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.05</v>
       </c>
       <c r="I307" t="n">
-        <v>0.1789</v>
+        <v>0.1783</v>
       </c>
       <c r="J307" t="n">
-        <v>3.578</v>
+        <v>3.566</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>0.97</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.0456</v>
+        <v>-0.0459</v>
       </c>
       <c r="J308" t="n">
-        <v>-0.912</v>
+        <v>-0.918</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>0.84</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1991</v>
+        <v>-0.1993</v>
       </c>
       <c r="J309" t="n">
-        <v>-3.982</v>
+        <v>-3.986</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.8</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2388</v>
+        <v>-0.2389</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.776</v>
+        <v>-4.778</v>
       </c>
     </row>
     <row r="311">
@@ -16626,13 +16626,13 @@
         <v>20</v>
       </c>
       <c r="H311" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4062</v>
+        <v>-0.3975</v>
       </c>
       <c r="J311" t="n">
-        <v>-8.124000000000001</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="312">
@@ -17666,13 +17666,13 @@
         <v>21</v>
       </c>
       <c r="H337" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I337" t="n">
-        <v>1.3987</v>
+        <v>1.4109</v>
       </c>
       <c r="J337" t="n">
-        <v>29.3727</v>
+        <v>29.6289</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.53</v>
       </c>
       <c r="I338" t="n">
-        <v>1.1363</v>
+        <v>1.1359</v>
       </c>
       <c r="J338" t="n">
-        <v>23.8623</v>
+        <v>23.8539</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.25</v>
       </c>
       <c r="I339" t="n">
-        <v>0.6451</v>
+        <v>0.6449</v>
       </c>
       <c r="J339" t="n">
-        <v>13.5471</v>
+        <v>13.5429</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3044</v>
+        <v>-0.3047</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.3924</v>
+        <v>-6.3987</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.77</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6999</v>
+        <v>-0.7002</v>
       </c>
       <c r="J341" t="n">
-        <v>-14.6979</v>
+        <v>-14.7042</v>
       </c>
     </row>
     <row r="342">
@@ -20469,10 +20469,10 @@
         <v>1.4</v>
       </c>
       <c r="I407" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7629</v>
       </c>
       <c r="J407" t="n">
-        <v>16.7992</v>
+        <v>16.7838</v>
       </c>
     </row>
     <row r="408">
@@ -20506,13 +20506,13 @@
         <v>22</v>
       </c>
       <c r="H408" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I408" t="n">
-        <v>0.0478</v>
+        <v>0.0779</v>
       </c>
       <c r="J408" t="n">
-        <v>1.0516</v>
+        <v>1.7138</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1</v>
       </c>
       <c r="I409" t="n">
-        <v>0.0038</v>
+        <v>0.0035</v>
       </c>
       <c r="J409" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.73</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3165</v>
+        <v>-0.3167</v>
       </c>
       <c r="J410" t="n">
-        <v>-6.963</v>
+        <v>-6.9674</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.68</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3627</v>
+        <v>-0.3629</v>
       </c>
       <c r="J411" t="n">
-        <v>-7.9794</v>
+        <v>-7.9838</v>
       </c>
     </row>
     <row r="412">
@@ -21269,10 +21269,10 @@
         <v>1.12</v>
       </c>
       <c r="I427" t="n">
-        <v>0.3074</v>
+        <v>0.3056</v>
       </c>
       <c r="J427" t="n">
-        <v>4.9184</v>
+        <v>4.8896</v>
       </c>
     </row>
     <row r="428">
@@ -21306,13 +21306,13 @@
         <v>16</v>
       </c>
       <c r="H428" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="I428" t="n">
-        <v>-0.1599</v>
+        <v>-0.1379</v>
       </c>
       <c r="J428" t="n">
-        <v>-2.5584</v>
+        <v>-2.2064</v>
       </c>
     </row>
     <row r="429">
@@ -21349,10 +21349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I429" t="n">
-        <v>-0.2138</v>
+        <v>-0.2144</v>
       </c>
       <c r="J429" t="n">
-        <v>-3.4208</v>
+        <v>-3.4304</v>
       </c>
     </row>
     <row r="430">
@@ -21389,10 +21389,10 @@
         <v>0.54</v>
       </c>
       <c r="I430" t="n">
-        <v>-0.4602</v>
+        <v>-0.4607</v>
       </c>
       <c r="J430" t="n">
-        <v>-7.3632</v>
+        <v>-7.3712</v>
       </c>
     </row>
     <row r="431">
@@ -21429,10 +21429,10 @@
         <v>0.22</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.7357</v>
+        <v>-0.736</v>
       </c>
       <c r="J431" t="n">
-        <v>-11.7712</v>
+        <v>-11.776</v>
       </c>
     </row>
     <row r="432">
@@ -22266,13 +22266,13 @@
         <v>22</v>
       </c>
       <c r="H452" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I452" t="n">
-        <v>1.6139</v>
+        <v>1.6021</v>
       </c>
       <c r="J452" t="n">
-        <v>35.5058</v>
+        <v>35.2462</v>
       </c>
     </row>
     <row r="453">
@@ -22309,10 +22309,10 @@
         <v>1.74</v>
       </c>
       <c r="I453" t="n">
-        <v>1.4125</v>
+        <v>1.4131</v>
       </c>
       <c r="J453" t="n">
-        <v>31.075</v>
+        <v>31.0882</v>
       </c>
     </row>
     <row r="454">
@@ -22349,10 +22349,10 @@
         <v>0.97</v>
       </c>
       <c r="I454" t="n">
-        <v>-0.1781</v>
+        <v>-0.1778</v>
       </c>
       <c r="J454" t="n">
-        <v>-3.9182</v>
+        <v>-3.9116</v>
       </c>
     </row>
     <row r="455">
@@ -22389,10 +22389,10 @@
         <v>0.85</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5133</v>
       </c>
       <c r="J455" t="n">
-        <v>-11.2992</v>
+        <v>-11.2926</v>
       </c>
     </row>
     <row r="456">
@@ -22429,10 +22429,10 @@
         <v>0.73</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.7865</v>
       </c>
       <c r="J456" t="n">
-        <v>-17.3096</v>
+        <v>-17.303</v>
       </c>
     </row>
     <row r="457">
@@ -23266,13 +23266,13 @@
         <v>24</v>
       </c>
       <c r="H477" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I477" t="n">
-        <v>0.6897</v>
+        <v>0.6994</v>
       </c>
       <c r="J477" t="n">
-        <v>16.5528</v>
+        <v>16.7856</v>
       </c>
     </row>
     <row r="478">
@@ -23309,10 +23309,10 @@
         <v>1.34</v>
       </c>
       <c r="I478" t="n">
-        <v>0.4597</v>
+        <v>0.4595</v>
       </c>
       <c r="J478" t="n">
-        <v>11.0328</v>
+        <v>11.028</v>
       </c>
     </row>
     <row r="479">
@@ -23349,10 +23349,10 @@
         <v>1.2</v>
       </c>
       <c r="I479" t="n">
-        <v>0.3003</v>
+        <v>0.3002</v>
       </c>
       <c r="J479" t="n">
-        <v>7.2072</v>
+        <v>7.2048</v>
       </c>
     </row>
     <row r="480">
@@ -23389,10 +23389,10 @@
         <v>1.14</v>
       </c>
       <c r="I480" t="n">
-        <v>0.2266</v>
+        <v>0.2265</v>
       </c>
       <c r="J480" t="n">
-        <v>5.4384</v>
+        <v>5.436</v>
       </c>
     </row>
     <row r="481">
@@ -23429,10 +23429,10 @@
         <v>0.65</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.4063</v>
+        <v>-0.4065</v>
       </c>
       <c r="J481" t="n">
-        <v>-9.751200000000001</v>
+        <v>-9.756</v>
       </c>
     </row>
     <row r="482">
@@ -26069,10 +26069,10 @@
         <v>2.19</v>
       </c>
       <c r="I547" t="n">
-        <v>1.8764</v>
+        <v>1.8768</v>
       </c>
       <c r="J547" t="n">
-        <v>28.146</v>
+        <v>28.152</v>
       </c>
     </row>
     <row r="548">
@@ -26109,10 +26109,10 @@
         <v>1.68</v>
       </c>
       <c r="I548" t="n">
-        <v>1.2823</v>
+        <v>1.2825</v>
       </c>
       <c r="J548" t="n">
-        <v>19.2345</v>
+        <v>19.2375</v>
       </c>
     </row>
     <row r="549">
@@ -26149,10 +26149,10 @@
         <v>1.57</v>
       </c>
       <c r="I549" t="n">
-        <v>1.1473</v>
+        <v>1.1475</v>
       </c>
       <c r="J549" t="n">
-        <v>17.2095</v>
+        <v>17.2125</v>
       </c>
     </row>
     <row r="550">
@@ -26186,13 +26186,13 @@
         <v>15</v>
       </c>
       <c r="H550" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I550" t="n">
-        <v>1.0326</v>
+        <v>1.0183</v>
       </c>
       <c r="J550" t="n">
-        <v>15.489</v>
+        <v>15.2745</v>
       </c>
     </row>
     <row r="551">
@@ -26229,10 +26229,10 @@
         <v>0.78</v>
       </c>
       <c r="I551" t="n">
-        <v>-0.7168</v>
+        <v>-0.7165</v>
       </c>
       <c r="J551" t="n">
-        <v>-10.752</v>
+        <v>-10.7475</v>
       </c>
     </row>
     <row r="552">
@@ -26669,10 +26669,10 @@
         <v>1.03</v>
       </c>
       <c r="I562" t="n">
-        <v>0.162</v>
+        <v>0.1612</v>
       </c>
       <c r="J562" t="n">
-        <v>2.592</v>
+        <v>2.5792</v>
       </c>
     </row>
     <row r="563">
@@ -26709,10 +26709,10 @@
         <v>0.87</v>
       </c>
       <c r="I563" t="n">
-        <v>-0.1572</v>
+        <v>-0.1576</v>
       </c>
       <c r="J563" t="n">
-        <v>-2.5152</v>
+        <v>-2.5216</v>
       </c>
     </row>
     <row r="564">
@@ -26746,13 +26746,13 @@
         <v>16</v>
       </c>
       <c r="H564" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I564" t="n">
-        <v>-0.25</v>
+        <v>-0.2407</v>
       </c>
       <c r="J564" t="n">
-        <v>-4</v>
+        <v>-3.8512</v>
       </c>
     </row>
     <row r="565">
@@ -26789,10 +26789,10 @@
         <v>0.63</v>
       </c>
       <c r="I565" t="n">
-        <v>-0.3862</v>
+        <v>-0.3865</v>
       </c>
       <c r="J565" t="n">
-        <v>-6.1792</v>
+        <v>-6.184</v>
       </c>
     </row>
     <row r="566">
@@ -26829,10 +26829,10 @@
         <v>0.48</v>
       </c>
       <c r="I566" t="n">
-        <v>-0.5184</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J566" t="n">
-        <v>-8.2944</v>
+        <v>-8.297599999999999</v>
       </c>
     </row>
     <row r="567">
@@ -26909,10 +26909,10 @@
         <v>1.61</v>
       </c>
       <c r="I568" t="n">
-        <v>1.2033</v>
+        <v>1.2036</v>
       </c>
       <c r="J568" t="n">
-        <v>19.2528</v>
+        <v>19.2576</v>
       </c>
     </row>
     <row r="569">
@@ -26949,10 +26949,10 @@
         <v>1.39</v>
       </c>
       <c r="I569" t="n">
-        <v>0.8905</v>
+        <v>0.8908</v>
       </c>
       <c r="J569" t="n">
-        <v>14.248</v>
+        <v>14.2528</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>1.29</v>
       </c>
       <c r="I570" t="n">
-        <v>0.6967</v>
+        <v>0.697</v>
       </c>
       <c r="J570" t="n">
-        <v>11.1472</v>
+        <v>11.152</v>
       </c>
     </row>
     <row r="571">
@@ -27026,13 +27026,13 @@
         <v>16</v>
       </c>
       <c r="H571" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.6646</v>
+        <v>-0.6869</v>
       </c>
       <c r="J571" t="n">
-        <v>-10.6336</v>
+        <v>-10.9904</v>
       </c>
     </row>
     <row r="572">
@@ -27469,10 +27469,10 @@
         <v>1.59</v>
       </c>
       <c r="I582" t="n">
-        <v>1.2113</v>
+        <v>1.2109</v>
       </c>
       <c r="J582" t="n">
-        <v>25.4373</v>
+        <v>25.4289</v>
       </c>
     </row>
     <row r="583">
@@ -27509,10 +27509,10 @@
         <v>1.27</v>
       </c>
       <c r="I583" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6829</v>
       </c>
       <c r="J583" t="n">
-        <v>14.343</v>
+        <v>14.3409</v>
       </c>
     </row>
     <row r="584">
@@ -27546,13 +27546,13 @@
         <v>21</v>
       </c>
       <c r="H584" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I584" t="n">
-        <v>0.5807</v>
+        <v>0.6016</v>
       </c>
       <c r="J584" t="n">
-        <v>12.1947</v>
+        <v>12.6336</v>
       </c>
     </row>
     <row r="585">
@@ -27589,10 +27589,10 @@
         <v>1.21</v>
       </c>
       <c r="I585" t="n">
-        <v>0.5592</v>
+        <v>0.5589</v>
       </c>
       <c r="J585" t="n">
-        <v>11.7432</v>
+        <v>11.7369</v>
       </c>
     </row>
     <row r="586">
@@ -27629,10 +27629,10 @@
         <v>1.04</v>
       </c>
       <c r="I586" t="n">
-        <v>0.1266</v>
+        <v>0.1262</v>
       </c>
       <c r="J586" t="n">
-        <v>2.6586</v>
+        <v>2.6502</v>
       </c>
     </row>
     <row r="587">
@@ -28669,10 +28669,10 @@
         <v>1.6</v>
       </c>
       <c r="I612" t="n">
-        <v>1.0229</v>
+        <v>1.0235</v>
       </c>
       <c r="J612" t="n">
-        <v>24.5496</v>
+        <v>24.564</v>
       </c>
     </row>
     <row r="613">
@@ -28709,10 +28709,10 @@
         <v>1.06</v>
       </c>
       <c r="I613" t="n">
-        <v>0.1676</v>
+        <v>0.1678</v>
       </c>
       <c r="J613" t="n">
-        <v>4.0224</v>
+        <v>4.0272</v>
       </c>
     </row>
     <row r="614">
@@ -28746,13 +28746,13 @@
         <v>24</v>
       </c>
       <c r="H614" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I614" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.1003</v>
       </c>
       <c r="J614" t="n">
-        <v>-2.1</v>
+        <v>-2.4072</v>
       </c>
     </row>
     <row r="615">
@@ -28789,10 +28789,10 @@
         <v>0.88</v>
       </c>
       <c r="I615" t="n">
-        <v>-0.1709</v>
+        <v>-0.1707</v>
       </c>
       <c r="J615" t="n">
-        <v>-4.1016</v>
+        <v>-4.0968</v>
       </c>
     </row>
     <row r="616">
@@ -28829,10 +28829,10 @@
         <v>0.6</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.4387</v>
+        <v>-0.4385</v>
       </c>
       <c r="J616" t="n">
-        <v>-10.5288</v>
+        <v>-10.524</v>
       </c>
     </row>
     <row r="617">
@@ -28869,10 +28869,10 @@
         <v>1.59</v>
       </c>
       <c r="I617" t="n">
-        <v>1.2365</v>
+        <v>1.236</v>
       </c>
       <c r="J617" t="n">
-        <v>29.676</v>
+        <v>29.664</v>
       </c>
     </row>
     <row r="618">
@@ -28909,10 +28909,10 @@
         <v>1.3</v>
       </c>
       <c r="I618" t="n">
-        <v>0.7613</v>
+        <v>0.7608</v>
       </c>
       <c r="J618" t="n">
-        <v>18.2712</v>
+        <v>18.2592</v>
       </c>
     </row>
     <row r="619">
@@ -28949,10 +28949,10 @@
         <v>1.01</v>
       </c>
       <c r="I619" t="n">
-        <v>0.0333</v>
+        <v>0.033</v>
       </c>
       <c r="J619" t="n">
-        <v>0.7992</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="620">
@@ -28986,13 +28986,13 @@
         <v>24</v>
       </c>
       <c r="H620" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I620" t="n">
-        <v>-0.1644</v>
+        <v>-0.1281</v>
       </c>
       <c r="J620" t="n">
-        <v>-3.9456</v>
+        <v>-3.0744</v>
       </c>
     </row>
     <row r="621">
@@ -29029,10 +29029,10 @@
         <v>0.93</v>
       </c>
       <c r="I621" t="n">
-        <v>-0.2899</v>
+        <v>-0.2903</v>
       </c>
       <c r="J621" t="n">
-        <v>-6.9576</v>
+        <v>-6.9672</v>
       </c>
     </row>
     <row r="622">
@@ -29866,13 +29866,13 @@
         <v>16</v>
       </c>
       <c r="H642" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I642" t="n">
-        <v>1.4128</v>
+        <v>1.4001</v>
       </c>
       <c r="J642" t="n">
-        <v>22.6048</v>
+        <v>22.4016</v>
       </c>
     </row>
     <row r="643">
@@ -29906,13 +29906,13 @@
         <v>16</v>
       </c>
       <c r="H643" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="I643" t="n">
-        <v>0.8617</v>
+        <v>0.8983</v>
       </c>
       <c r="J643" t="n">
-        <v>13.7872</v>
+        <v>14.3728</v>
       </c>
     </row>
     <row r="644">
@@ -29949,10 +29949,10 @@
         <v>1.36</v>
       </c>
       <c r="I644" t="n">
-        <v>0.843</v>
+        <v>0.8428</v>
       </c>
       <c r="J644" t="n">
-        <v>13.488</v>
+        <v>13.4848</v>
       </c>
     </row>
     <row r="645">
@@ -29989,10 +29989,10 @@
         <v>1.29</v>
       </c>
       <c r="I645" t="n">
-        <v>0.7068</v>
+        <v>0.7065</v>
       </c>
       <c r="J645" t="n">
-        <v>11.3088</v>
+        <v>11.304</v>
       </c>
     </row>
     <row r="646">
@@ -30029,10 +30029,10 @@
         <v>1.23</v>
       </c>
       <c r="I646" t="n">
-        <v>0.5823</v>
+        <v>0.582</v>
       </c>
       <c r="J646" t="n">
-        <v>9.316800000000001</v>
+        <v>9.311999999999999</v>
       </c>
     </row>
     <row r="647">
@@ -30266,7 +30266,7 @@
         <v>14</v>
       </c>
       <c r="H652" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="I652" t="n">
         <v>1.9372</v>
@@ -30309,10 +30309,10 @@
         <v>2.23</v>
       </c>
       <c r="I653" t="n">
-        <v>1.8932</v>
+        <v>1.8935</v>
       </c>
       <c r="J653" t="n">
-        <v>26.5048</v>
+        <v>26.509</v>
       </c>
     </row>
     <row r="654">
@@ -30349,10 +30349,10 @@
         <v>1.63</v>
       </c>
       <c r="I654" t="n">
-        <v>1.2117</v>
+        <v>1.2118</v>
       </c>
       <c r="J654" t="n">
-        <v>16.9638</v>
+        <v>16.9652</v>
       </c>
     </row>
     <row r="655">
@@ -30389,10 +30389,10 @@
         <v>1.42</v>
       </c>
       <c r="I655" t="n">
-        <v>0.92</v>
+        <v>0.9202</v>
       </c>
       <c r="J655" t="n">
-        <v>12.88</v>
+        <v>12.8828</v>
       </c>
     </row>
     <row r="656">
@@ -30429,10 +30429,10 @@
         <v>0.65</v>
       </c>
       <c r="I656" t="n">
-        <v>-1.0016</v>
+        <v>-1.0014</v>
       </c>
       <c r="J656" t="n">
-        <v>-14.0224</v>
+        <v>-14.0196</v>
       </c>
     </row>
     <row r="657">
@@ -31069,10 +31069,10 @@
         <v>1.76</v>
       </c>
       <c r="I672" t="n">
-        <v>1.4182</v>
+        <v>1.4186</v>
       </c>
       <c r="J672" t="n">
-        <v>26.9458</v>
+        <v>26.9534</v>
       </c>
     </row>
     <row r="673">
@@ -31109,10 +31109,10 @@
         <v>1.47</v>
       </c>
       <c r="I673" t="n">
-        <v>1.0407</v>
+        <v>1.041</v>
       </c>
       <c r="J673" t="n">
-        <v>19.7733</v>
+        <v>19.779</v>
       </c>
     </row>
     <row r="674">
@@ -31146,13 +31146,13 @@
         <v>19</v>
       </c>
       <c r="H674" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I674" t="n">
-        <v>1.0106</v>
+        <v>0.9951</v>
       </c>
       <c r="J674" t="n">
-        <v>19.2014</v>
+        <v>18.9069</v>
       </c>
     </row>
     <row r="675">
@@ -31189,10 +31189,10 @@
         <v>1.34</v>
       </c>
       <c r="I675" t="n">
-        <v>0.8135</v>
+        <v>0.8137</v>
       </c>
       <c r="J675" t="n">
-        <v>15.4565</v>
+        <v>15.4603</v>
       </c>
     </row>
     <row r="676">
@@ -31229,10 +31229,10 @@
         <v>0.57</v>
       </c>
       <c r="I676" t="n">
-        <v>-1.1241</v>
+        <v>-1.1239</v>
       </c>
       <c r="J676" t="n">
-        <v>-21.3579</v>
+        <v>-21.3541</v>
       </c>
     </row>
     <row r="677">
@@ -33269,10 +33269,10 @@
         <v>1.58</v>
       </c>
       <c r="I727" t="n">
-        <v>1.0282</v>
+        <v>1.029</v>
       </c>
       <c r="J727" t="n">
-        <v>24.6768</v>
+        <v>24.696</v>
       </c>
     </row>
     <row r="728">
@@ -33309,10 +33309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I728" t="n">
-        <v>-0.2367</v>
+        <v>-0.2365</v>
       </c>
       <c r="J728" t="n">
-        <v>-5.6808</v>
+        <v>-5.676</v>
       </c>
     </row>
     <row r="729">
@@ -33346,13 +33346,13 @@
         <v>24</v>
       </c>
       <c r="H729" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I729" t="n">
-        <v>-0.2466</v>
+        <v>-0.2563</v>
       </c>
       <c r="J729" t="n">
-        <v>-5.9184</v>
+        <v>-6.1512</v>
       </c>
     </row>
     <row r="730">
@@ -33389,10 +33389,10 @@
         <v>0.76</v>
       </c>
       <c r="I730" t="n">
-        <v>-0.2856</v>
+        <v>-0.2854</v>
       </c>
       <c r="J730" t="n">
-        <v>-6.8544</v>
+        <v>-6.8496</v>
       </c>
     </row>
     <row r="731">
@@ -33429,10 +33429,10 @@
         <v>0.74</v>
       </c>
       <c r="I731" t="n">
-        <v>-0.3046</v>
+        <v>-0.3044</v>
       </c>
       <c r="J731" t="n">
-        <v>-7.3104</v>
+        <v>-7.3056</v>
       </c>
     </row>
     <row r="732">
@@ -34266,13 +34266,13 @@
         <v>15</v>
       </c>
       <c r="H752" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="I752" t="n">
-        <v>1.8618</v>
+        <v>1.851</v>
       </c>
       <c r="J752" t="n">
-        <v>27.927</v>
+        <v>27.765</v>
       </c>
     </row>
     <row r="753">
@@ -34309,10 +34309,10 @@
         <v>1.67</v>
       </c>
       <c r="I753" t="n">
-        <v>1.2684</v>
+        <v>1.2686</v>
       </c>
       <c r="J753" t="n">
-        <v>19.026</v>
+        <v>19.029</v>
       </c>
     </row>
     <row r="754">
@@ -34349,10 +34349,10 @@
         <v>1.58</v>
       </c>
       <c r="I754" t="n">
-        <v>1.1585</v>
+        <v>1.1586</v>
       </c>
       <c r="J754" t="n">
-        <v>17.3775</v>
+        <v>17.379</v>
       </c>
     </row>
     <row r="755">
@@ -34389,10 +34389,10 @@
         <v>1.24</v>
       </c>
       <c r="I755" t="n">
-        <v>0.5821</v>
+        <v>0.5823</v>
       </c>
       <c r="J755" t="n">
-        <v>8.7315</v>
+        <v>8.734500000000001</v>
       </c>
     </row>
     <row r="756">
@@ -34429,10 +34429,10 @@
         <v>1.11</v>
       </c>
       <c r="I756" t="n">
-        <v>0.282</v>
+        <v>0.2823</v>
       </c>
       <c r="J756" t="n">
-        <v>4.23</v>
+        <v>4.2345</v>
       </c>
     </row>
     <row r="757">
@@ -34466,13 +34466,13 @@
         <v>15</v>
       </c>
       <c r="H757" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I757" t="n">
-        <v>-0.153</v>
+        <v>-0.142</v>
       </c>
       <c r="J757" t="n">
-        <v>-2.295</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="758">
@@ -34509,10 +34509,10 @@
         <v>0.79</v>
       </c>
       <c r="I758" t="n">
-        <v>-0.209</v>
+        <v>-0.2096</v>
       </c>
       <c r="J758" t="n">
-        <v>-3.135</v>
+        <v>-3.144</v>
       </c>
     </row>
     <row r="759">
@@ -34549,10 +34549,10 @@
         <v>0.52</v>
       </c>
       <c r="I759" t="n">
-        <v>-0.4616</v>
+        <v>-0.4619</v>
       </c>
       <c r="J759" t="n">
-        <v>-6.924</v>
+        <v>-6.9285</v>
       </c>
     </row>
     <row r="760">
@@ -34589,10 +34589,10 @@
         <v>0.46</v>
       </c>
       <c r="I760" t="n">
-        <v>-0.5144</v>
+        <v>-0.5147</v>
       </c>
       <c r="J760" t="n">
-        <v>-7.716</v>
+        <v>-7.7205</v>
       </c>
     </row>
     <row r="761">
@@ -34629,10 +34629,10 @@
         <v>0.36</v>
       </c>
       <c r="I761" t="n">
-        <v>-0.6028</v>
+        <v>-0.603</v>
       </c>
       <c r="J761" t="n">
-        <v>-9.042</v>
+        <v>-9.045</v>
       </c>
     </row>
     <row r="762">
@@ -34669,10 +34669,10 @@
         <v>1.47</v>
       </c>
       <c r="I762" t="n">
-        <v>1.0945</v>
+        <v>1.0933</v>
       </c>
       <c r="J762" t="n">
-        <v>32.835</v>
+        <v>32.799</v>
       </c>
     </row>
     <row r="763">
@@ -34706,13 +34706,13 @@
         <v>30</v>
       </c>
       <c r="H763" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I763" t="n">
-        <v>0.7845</v>
+        <v>0.8042</v>
       </c>
       <c r="J763" t="n">
-        <v>23.535</v>
+        <v>24.126</v>
       </c>
     </row>
     <row r="764">
@@ -34749,10 +34749,10 @@
         <v>0.98</v>
       </c>
       <c r="I764" t="n">
-        <v>-0.1116</v>
+        <v>-0.1124</v>
       </c>
       <c r="J764" t="n">
-        <v>-3.348</v>
+        <v>-3.372</v>
       </c>
     </row>
     <row r="765">
@@ -34789,10 +34789,10 @@
         <v>0.97</v>
       </c>
       <c r="I765" t="n">
-        <v>-0.1481</v>
+        <v>-0.1489</v>
       </c>
       <c r="J765" t="n">
-        <v>-4.443</v>
+        <v>-4.467</v>
       </c>
     </row>
     <row r="766">
@@ -34826,13 +34826,13 @@
         <v>30</v>
       </c>
       <c r="H766" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I766" t="n">
-        <v>-0.9488</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="J766" t="n">
-        <v>-28.464</v>
+        <v>-27.867</v>
       </c>
     </row>
     <row r="767">
@@ -35669,10 +35669,10 @@
         <v>1.15</v>
       </c>
       <c r="I787" t="n">
-        <v>0.4094</v>
+        <v>0.4103</v>
       </c>
       <c r="J787" t="n">
-        <v>8.5974</v>
+        <v>8.616300000000001</v>
       </c>
     </row>
     <row r="788">
@@ -35709,10 +35709,10 @@
         <v>0.86</v>
       </c>
       <c r="I788" t="n">
-        <v>-0.1735</v>
+        <v>-0.1733</v>
       </c>
       <c r="J788" t="n">
-        <v>-3.6435</v>
+        <v>-3.6393</v>
       </c>
     </row>
     <row r="789">
@@ -35749,10 +35749,10 @@
         <v>0.77</v>
       </c>
       <c r="I789" t="n">
-        <v>-0.262</v>
+        <v>-0.2619</v>
       </c>
       <c r="J789" t="n">
-        <v>-5.502</v>
+        <v>-5.4999</v>
       </c>
     </row>
     <row r="790">
@@ -35786,13 +35786,13 @@
         <v>21</v>
       </c>
       <c r="H790" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I790" t="n">
-        <v>-0.3907</v>
+        <v>-0.3994</v>
       </c>
       <c r="J790" t="n">
-        <v>-8.204700000000001</v>
+        <v>-8.3874</v>
       </c>
     </row>
     <row r="791">
@@ -35829,10 +35829,10 @@
         <v>0.57</v>
       </c>
       <c r="I791" t="n">
-        <v>-0.444</v>
+        <v>-0.4438</v>
       </c>
       <c r="J791" t="n">
-        <v>-9.324</v>
+        <v>-9.319800000000001</v>
       </c>
     </row>
     <row r="792">
@@ -35866,13 +35866,13 @@
         <v>19</v>
       </c>
       <c r="H792" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I792" t="n">
-        <v>0.9687</v>
+        <v>0.981</v>
       </c>
       <c r="J792" t="n">
-        <v>18.4053</v>
+        <v>18.639</v>
       </c>
     </row>
     <row r="793">
@@ -35909,10 +35909,10 @@
         <v>1.1</v>
       </c>
       <c r="I793" t="n">
-        <v>0.26</v>
+        <v>0.2595</v>
       </c>
       <c r="J793" t="n">
-        <v>4.94</v>
+        <v>4.9305</v>
       </c>
     </row>
     <row r="794">
@@ -35949,10 +35949,10 @@
         <v>0.91</v>
       </c>
       <c r="I794" t="n">
-        <v>-0.1323</v>
+        <v>-0.1324</v>
       </c>
       <c r="J794" t="n">
-        <v>-2.5137</v>
+        <v>-2.5156</v>
       </c>
     </row>
     <row r="795">
@@ -35989,10 +35989,10 @@
         <v>0.84</v>
       </c>
       <c r="I795" t="n">
-        <v>-0.2084</v>
+        <v>-0.2086</v>
       </c>
       <c r="J795" t="n">
-        <v>-3.9596</v>
+        <v>-3.9634</v>
       </c>
     </row>
     <row r="796">
@@ -36029,10 +36029,10 @@
         <v>0.42</v>
       </c>
       <c r="I796" t="n">
-        <v>-0.587</v>
+        <v>-0.5871</v>
       </c>
       <c r="J796" t="n">
-        <v>-11.153</v>
+        <v>-11.1549</v>
       </c>
     </row>
     <row r="797">
@@ -36266,13 +36266,13 @@
         <v>24</v>
       </c>
       <c r="H802" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I802" t="n">
-        <v>0.7004</v>
+        <v>0.7149</v>
       </c>
       <c r="J802" t="n">
-        <v>16.8096</v>
+        <v>17.1576</v>
       </c>
     </row>
     <row r="803">
@@ -36309,10 +36309,10 @@
         <v>1.11</v>
       </c>
       <c r="I803" t="n">
-        <v>0.2687</v>
+        <v>0.2683</v>
       </c>
       <c r="J803" t="n">
-        <v>6.4488</v>
+        <v>6.4392</v>
       </c>
     </row>
     <row r="804">
@@ -36349,10 +36349,10 @@
         <v>0.98</v>
       </c>
       <c r="I804" t="n">
-        <v>-0.0439</v>
+        <v>-0.044</v>
       </c>
       <c r="J804" t="n">
-        <v>-1.0536</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="805">
@@ -36389,10 +36389,10 @@
         <v>0.84</v>
       </c>
       <c r="I805" t="n">
-        <v>-0.2135</v>
+        <v>-0.2137</v>
       </c>
       <c r="J805" t="n">
-        <v>-5.124</v>
+        <v>-5.1288</v>
       </c>
     </row>
     <row r="806">
@@ -36429,10 +36429,10 @@
         <v>0.79</v>
       </c>
       <c r="I806" t="n">
-        <v>-0.2639</v>
+        <v>-0.2641</v>
       </c>
       <c r="J806" t="n">
-        <v>-6.3336</v>
+        <v>-6.3384</v>
       </c>
     </row>
     <row r="807">
@@ -38266,13 +38266,13 @@
         <v>22</v>
       </c>
       <c r="H852" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I852" t="n">
-        <v>0.61</v>
+        <v>0.5946</v>
       </c>
       <c r="J852" t="n">
-        <v>13.42</v>
+        <v>13.0812</v>
       </c>
     </row>
     <row r="853">
@@ -38309,10 +38309,10 @@
         <v>0.97</v>
       </c>
       <c r="I853" t="n">
-        <v>-0.056</v>
+        <v>-0.0558</v>
       </c>
       <c r="J853" t="n">
-        <v>-1.232</v>
+        <v>-1.2276</v>
       </c>
     </row>
     <row r="854">
@@ -38349,10 +38349,10 @@
         <v>0.91</v>
       </c>
       <c r="I854" t="n">
-        <v>-0.132</v>
+        <v>-0.1318</v>
       </c>
       <c r="J854" t="n">
-        <v>-2.904</v>
+        <v>-2.8996</v>
       </c>
     </row>
     <row r="855">
@@ -38389,10 +38389,10 @@
         <v>0.83</v>
       </c>
       <c r="I855" t="n">
-        <v>-0.2183</v>
+        <v>-0.2182</v>
       </c>
       <c r="J855" t="n">
-        <v>-4.8026</v>
+        <v>-4.8004</v>
       </c>
     </row>
     <row r="856">
@@ -38429,10 +38429,10 @@
         <v>0.78</v>
       </c>
       <c r="I856" t="n">
-        <v>-0.2682</v>
+        <v>-0.268</v>
       </c>
       <c r="J856" t="n">
-        <v>-5.9004</v>
+        <v>-5.896</v>
       </c>
     </row>
     <row r="857">
@@ -38669,10 +38669,10 @@
         <v>1.38</v>
       </c>
       <c r="I862" t="n">
-        <v>0.9147</v>
+        <v>0.9152</v>
       </c>
       <c r="J862" t="n">
-        <v>19.2087</v>
+        <v>19.2192</v>
       </c>
     </row>
     <row r="863">
@@ -38709,10 +38709,10 @@
         <v>1.3</v>
       </c>
       <c r="I863" t="n">
-        <v>0.7557</v>
+        <v>0.7561</v>
       </c>
       <c r="J863" t="n">
-        <v>15.8697</v>
+        <v>15.8781</v>
       </c>
     </row>
     <row r="864">
@@ -38749,10 +38749,10 @@
         <v>1.25</v>
       </c>
       <c r="I864" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.653</v>
       </c>
       <c r="J864" t="n">
-        <v>13.7067</v>
+        <v>13.713</v>
       </c>
     </row>
     <row r="865">
@@ -38786,13 +38786,13 @@
         <v>21</v>
       </c>
       <c r="H865" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="I865" t="n">
-        <v>0.1066</v>
+        <v>0.0704</v>
       </c>
       <c r="J865" t="n">
-        <v>2.2386</v>
+        <v>1.4784</v>
       </c>
     </row>
     <row r="866">
@@ -38829,10 +38829,10 @@
         <v>0.97</v>
       </c>
       <c r="I866" t="n">
-        <v>-0.169</v>
+        <v>-0.1687</v>
       </c>
       <c r="J866" t="n">
-        <v>-3.549</v>
+        <v>-3.5427</v>
       </c>
     </row>
     <row r="867">
@@ -40269,10 +40269,10 @@
         <v>1.28</v>
       </c>
       <c r="I902" t="n">
-        <v>0.7264</v>
+        <v>0.7259</v>
       </c>
       <c r="J902" t="n">
-        <v>17.4336</v>
+        <v>17.4216</v>
       </c>
     </row>
     <row r="903">
@@ -40309,10 +40309,10 @@
         <v>1.27</v>
       </c>
       <c r="I903" t="n">
-        <v>0.7055</v>
+        <v>0.705</v>
       </c>
       <c r="J903" t="n">
-        <v>16.932</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="904">
@@ -40349,10 +40349,10 @@
         <v>1.23</v>
       </c>
       <c r="I904" t="n">
-        <v>0.6202</v>
+        <v>0.6198</v>
       </c>
       <c r="J904" t="n">
-        <v>14.8848</v>
+        <v>14.8752</v>
       </c>
     </row>
     <row r="905">
@@ -40389,10 +40389,10 @@
         <v>0.95</v>
       </c>
       <c r="I905" t="n">
-        <v>-0.225</v>
+        <v>-0.2253</v>
       </c>
       <c r="J905" t="n">
-        <v>-5.4</v>
+        <v>-5.4072</v>
       </c>
     </row>
     <row r="906">
@@ -40426,13 +40426,13 @@
         <v>24</v>
       </c>
       <c r="H906" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I906" t="n">
-        <v>-0.2848</v>
+        <v>-0.2558</v>
       </c>
       <c r="J906" t="n">
-        <v>-6.8352</v>
+        <v>-6.1392</v>
       </c>
     </row>
     <row r="907">
@@ -40866,13 +40866,13 @@
         <v>22</v>
       </c>
       <c r="H917" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I917" t="n">
-        <v>0.2012</v>
+        <v>0.2219</v>
       </c>
       <c r="J917" t="n">
-        <v>4.4264</v>
+        <v>4.8818</v>
       </c>
     </row>
     <row r="918">
@@ -40909,10 +40909,10 @@
         <v>0.99</v>
       </c>
       <c r="I918" t="n">
-        <v>-0.0221</v>
+        <v>-0.0222</v>
       </c>
       <c r="J918" t="n">
-        <v>-0.4862</v>
+        <v>-0.4884</v>
       </c>
     </row>
     <row r="919">
@@ -40949,10 +40949,10 @@
         <v>0.95</v>
       </c>
       <c r="I919" t="n">
-        <v>-0.0828</v>
+        <v>-0.0829</v>
       </c>
       <c r="J919" t="n">
-        <v>-1.8216</v>
+        <v>-1.8238</v>
       </c>
     </row>
     <row r="920">
@@ -40989,10 +40989,10 @@
         <v>0.93</v>
       </c>
       <c r="I920" t="n">
-        <v>-0.1076</v>
+        <v>-0.1077</v>
       </c>
       <c r="J920" t="n">
-        <v>-2.3672</v>
+        <v>-2.3694</v>
       </c>
     </row>
     <row r="921">
@@ -41029,10 +41029,10 @@
         <v>0.8</v>
       </c>
       <c r="I921" t="n">
-        <v>-0.2476</v>
+        <v>-0.2478</v>
       </c>
       <c r="J921" t="n">
-        <v>-5.4472</v>
+        <v>-5.4516</v>
       </c>
     </row>
     <row r="922">
@@ -41266,13 +41266,13 @@
         <v>16</v>
       </c>
       <c r="H927" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I927" t="n">
-        <v>-0.1321</v>
+        <v>-0.1208</v>
       </c>
       <c r="J927" t="n">
-        <v>-2.1136</v>
+        <v>-1.9328</v>
       </c>
     </row>
     <row r="928">
@@ -41309,10 +41309,10 @@
         <v>0.7</v>
       </c>
       <c r="I928" t="n">
-        <v>-0.2956</v>
+        <v>-0.2961</v>
       </c>
       <c r="J928" t="n">
-        <v>-4.7296</v>
+        <v>-4.7376</v>
       </c>
     </row>
     <row r="929">
@@ -41349,10 +41349,10 @@
         <v>0.49</v>
       </c>
       <c r="I929" t="n">
-        <v>-0.4839</v>
+        <v>-0.4842</v>
       </c>
       <c r="J929" t="n">
-        <v>-7.7424</v>
+        <v>-7.7472</v>
       </c>
     </row>
     <row r="930">
@@ -41389,10 +41389,10 @@
         <v>0.43</v>
       </c>
       <c r="I930" t="n">
-        <v>-0.5369</v>
+        <v>-0.5372</v>
       </c>
       <c r="J930" t="n">
-        <v>-8.590400000000001</v>
+        <v>-8.5952</v>
       </c>
     </row>
     <row r="931">
@@ -41429,10 +41429,10 @@
         <v>0.37</v>
       </c>
       <c r="I931" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5905</v>
       </c>
       <c r="J931" t="n">
-        <v>-9.443199999999999</v>
+        <v>-9.448</v>
       </c>
     </row>
   </sheetData>
